--- a/plantilla-productos.xlsx
+++ b/plantilla-productos.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carta Sempertex" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$T$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$V$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="122">
     <fill>
       <patternFill/>
     </fill>
@@ -255,6 +256,431 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF5D8F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F3EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DF97B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B57981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DD3F84"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C42A52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9252F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A2D38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A2A35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D914"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4A83A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D19B40"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0083976A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001C9849"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0031AE76"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007AC345"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6548"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00234C5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0053A6A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0034A1B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E9FEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00213DA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2545"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A181C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00453D9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085357C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D96A77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7A785"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DB5F42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B35545"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9B391"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AE834C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E4B3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A3530"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001C1D24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0098989F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFE8EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6CCD1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBE99C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ACD5C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007BB9E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CAB9DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBB18C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBA89C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC2A7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EC1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0048C22A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF5A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDB1A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BCA4A2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008FC29D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00627D92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A7193"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F0EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBE5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DC7EAE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009EBB85"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0098C3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AB86C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B8BABF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECE8DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A88D99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0076A09C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006C86A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008C80AE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B39A72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCD5C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CF3868"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C62F2C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F8A44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4FBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1917E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CF994E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0024262A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8778A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0093307A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8302D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0084A23A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8466"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D6D9B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006745B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0644F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A3843C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B5A38C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B2B4B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -275,7 +701,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -349,6 +775,93 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -549,6 +1062,18 @@
       <text>
         <t>Otras palabras con las que los clientes buscan este producto.
 Ejemplo: metalico helio estrellas</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Para vender un producto en varios tamaños: haz una fila por tamaño con el MISMO nombre y escribe aquí el tamaño (5", 12", 18"). Cada fila lleva su precio, mayoreo, peso y presentación; en la tienda se ven como un solo producto con selector de tamaño.
+Ejemplo: 12"</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Colores o tonos sin existencia, separados por comas (nombres o códigos de la carta). En un producto con tamaños, aplica solo al tamaño de esa fila.
+Ejemplo: 015, 390</t>
       </text>
     </comment>
   </commentList>
@@ -844,7 +1369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -867,6 +1392,8 @@
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -968,6 +1495,16 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Palabras para buscar</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Colores agotados</t>
         </is>
       </c>
     </row>
@@ -1048,6 +1585,8 @@
           <t>estrella estrellas metalico helio</t>
         </is>
       </c>
+      <c r="U2" s="3" t="n"/>
+      <c r="V2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1126,6 +1665,8 @@
           <t>corazon corazones amor san valentin metalico helio</t>
         </is>
       </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1212,6 +1753,8 @@
           <t>numero numeros edad gigante cumpleaños aniversario</t>
         </is>
       </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1298,6 +1841,8 @@
           <t>numero numeros mini varita centro de mesa</t>
         </is>
       </c>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1384,6 +1929,8 @@
           <t>letra letras nombre frase abecedario</t>
         </is>
       </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1462,6 +2009,8 @@
           <t>feliz cumpleaños cumple redondo impreso</t>
         </is>
       </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1536,6 +2085,8 @@
           <t>burbuja bubble transparente cristal relleno</t>
         </is>
       </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1618,6 +2169,8 @@
           <t>bebe baby boy girl niño niña revelacion</t>
         </is>
       </c>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1696,6 +2249,8 @@
           <t>te amo corazon amor san valentin novia novio</t>
         </is>
       </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1770,6 +2325,8 @@
           <t>graduacion graduado birrete egresado felicidades</t>
         </is>
       </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1848,6 +2405,8 @@
           <t>feliz navidad navideño posada intercambio copos</t>
         </is>
       </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1922,6 +2481,8 @@
           <t>pino arbol arbolito navidad navideño posada</t>
         </is>
       </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2000,6 +2561,8 @@
           <t>esfera navidad navideño posada</t>
         </is>
       </c>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2082,6 +2645,8 @@
           <t>bouquet ramo kit juego set cumpleaños</t>
         </is>
       </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2160,6 +2725,8 @@
           <t>xv quince años quinceañera corona</t>
         </is>
       </c>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2234,6 +2801,8 @@
           <t>mexico fiestas patrias septiembre independencia tricolor noche mexicana</t>
         </is>
       </c>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2312,16 +2881,14 @@
           <t>estrella estrellitas mini varita centro de mesa</t>
         </is>
       </c>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>globo-latex-12-estandar-50</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" estándar, bolsa 50 pzas</t>
+          <t>Globo Sempertex redondo</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2331,39 +2898,39 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, Fiestas patrias, Graduación</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, XV años, Bodas y aniversarios, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 100 piezas</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Globo redondo de 12 pulgadas en color sólido, de látex natural. Es el más usado para arcos, columnas y decoración con aire o helio. Cada bolsa trae 50 piezas del mismo color.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Material: Látex natural biodegradable; Duración con helio: 8 a 12 horas (más con sellador)</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Fucsia, Lila, Morado, Azul rey, Azul cielo, Verde limón, Amarillo, Naranja, Blanco, Negro</t>
+          <t>Carta Sempertex</t>
         </is>
       </c>
       <c r="M19" s="3" t="n"/>
@@ -2377,7 +2944,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -2387,19 +2954,21 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>latex r12 12 pulgadas bolsa colores arco columna</t>
-        </is>
-      </c>
+          <t>sempertex latex redondo carta de colores tonos r5 r12 r18 arco</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>5"</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>globo-latex-12-pastel-50</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" pastel, bolsa 50 pzas</t>
+          <t>Globo Sempertex redondo</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2409,14 +2978,14 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Revelación de género, XV años, Bodas y aniversarios, Fiestas infantiles</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, XV años, Bodas y aniversarios, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>6</v>
@@ -2427,21 +2996,21 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Tonos pastel tipo macaron para decoraciones suaves: baby shower, bautizos y mesas de postres.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Pastel mate</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Rosa pastel, Lila pastel, Azul pastel, Menta, Amarillo pastel, Durazno</t>
+          <t>Carta Sempertex</t>
         </is>
       </c>
       <c r="M20" s="3" t="n"/>
@@ -2450,7 +3019,7 @@
       <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2465,19 +3034,21 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>latex pastel macaron baby bautizo</t>
-        </is>
-      </c>
+          <t>sempertex latex redondo carta de colores tonos r5 r12 r18 arco</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>globo-latex-12-metalico-50</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" metálico perlado, bolsa 50 pzas</t>
+          <t>Globo Sempertex redondo</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2487,39 +3058,39 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Graduación, Navidad, Cumpleaños</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, XV años, Bodas y aniversarios, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 25 piezas</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Acabado perlado con brillo suave. Combina muy bien con globos foil y decoraciones elegantes.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Metálico perlado</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Oro rosa, Azul, Rojo, Rosa, Morado, Verde</t>
+          <t>Carta Sempertex</t>
         </is>
       </c>
       <c r="M21" s="3" t="n"/>
@@ -2533,7 +3104,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -2543,19 +3114,25 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>latex metalico perlado brillo</t>
-        </is>
-      </c>
+          <t>sempertex latex redondo carta de colores tonos r5 r12 r18 arco</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>18"</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-12-cromado-25</t>
+          <t>globo-latex-12-estandar-50</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex cromado 12", bolsa 25 pzas</t>
+          <t>Globo de látex 12" estándar, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2565,39 +3142,39 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Graduación, Navidad</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, Fiestas patrias, Graduación</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 25 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Efecto espejo, parecido al foil pero en látex. Para decoraciones de lujo y arcos de evento.</t>
+          <t>Globo redondo de 12 pulgadas en color sólido, de látex natural. Es el más usado para arcos, columnas y decoración con aire o helio. Cada bolsa trae 50 piezas del mismo color.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 25 piezas; Acabado: Cromado tipo espejo</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Material: Látex natural biodegradable; Duración con helio: 8 a 12 horas (más con sellador)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Oro cromo #c9a227, Plata cromo #a9b1bb, Oro rosa cromo #d9897a, Champagne cromo #d8c08f, Azul cromo #3767c9</t>
+          <t>Rojo, Rosa, Fucsia, Lila, Morado, Azul rey, Azul cielo, Verde limón, Amarillo, Naranja, Blanco, Negro</t>
         </is>
       </c>
       <c r="M22" s="3" t="n"/>
@@ -2606,14 +3183,14 @@
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -2621,19 +3198,21 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>latex cromado cromo espejo lujo</t>
-        </is>
-      </c>
+          <t>latex r12 12 pulgadas bolsa colores arco columna</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-5-mini-100</t>
+          <t>globo-latex-12-pastel-50</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 5" mini, bolsa 100 pzas</t>
+          <t>Globo de látex 12" pastel, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2643,39 +3222,39 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Cumpleaños, Bodas y aniversarios</t>
+          <t>Baby shower, Revelación de género, XV años, Bodas y aniversarios, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 100 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Globito de 5 pulgadas para dar textura a arcos orgánicos, rellenar burbujas y decorar mesas.</t>
+          <t>Tonos pastel tipo macaron para decoraciones suaves: baby shower, bautizos y mesas de postres.</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Medida: 5 in (13 cm) inflado; Contenido: 100 piezas; Material: Látex natural</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Pastel mate</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Rosa, Rojo, Azul rey, Verde limón, Lila, Amarillo, Blanco, Negro</t>
+          <t>Rosa pastel, Lila pastel, Azul pastel, Menta, Amarillo pastel, Durazno</t>
         </is>
       </c>
       <c r="M23" s="3" t="n"/>
@@ -2689,7 +3268,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -2699,19 +3278,21 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>latex mini 5 pulgadas chico arco organico relleno</t>
-        </is>
-      </c>
+          <t>latex pastel macaron baby bautizo</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-18-10</t>
+          <t>globo-latex-12-metalico-50</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 18", bolsa 10 pzas</t>
+          <t>Globo de látex 12" metálico perlado, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2721,39 +3302,39 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+          <t>Bodas y aniversarios, XV años, Graduación, Navidad, Cumpleaños</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Globo grande de 18 pulgadas para dar volumen en arcos y columnas.</t>
+          <t>Acabado perlado con brillo suave. Combina muy bien con globos foil y decoraciones elegantes.</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Medida: 18 in (45 cm) inflado; Contenido: 10 piezas; Material: Látex natural</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Metálico perlado</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Azul cielo, Rosa, Rojo, Amarillo, Blanco, Negro</t>
+          <t>Dorado, Plateado, Oro rosa, Azul, Rojo, Rosa, Morado, Verde</t>
         </is>
       </c>
       <c r="M24" s="3" t="n"/>
@@ -2762,14 +3343,14 @@
       <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -2777,19 +3358,21 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>latex 18 pulgadas grande arco columna</t>
-        </is>
-      </c>
+          <t>latex metalico perlado brillo</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="n"/>
+      <c r="V24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-260-50</t>
+          <t>globo-latex-12-cromado-25</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 260 para figuras, bolsa 50 pzas</t>
+          <t>Globo de látex cromado 12", bolsa 25 pzas</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2799,39 +3382,39 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Fiestas infantiles, Cumpleaños</t>
+          <t>Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 25 piezas</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Globo largo para hacer perritos, espadas, flores y figuras. Se infla con inflador manual.</t>
+          <t>Efecto espejo, parecido al foil pero en látex. Para decoraciones de lujo y arcos de evento.</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Medida: 5 × 150 cm inflado (260Q); Contenido: 50 piezas; Inflado: Con inflador manual</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 25 piezas; Acabado: Cromado tipo espejo</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Surtido, Blanco, Rojo, Azul, Verde, Amarillo, Negro</t>
+          <t>Oro cromo #c9a227, Plata cromo #a9b1bb, Oro rosa cromo #d9897a, Champagne cromo #d8c08f, Azul cromo #3767c9</t>
         </is>
       </c>
       <c r="M25" s="3" t="n"/>
@@ -2855,19 +3438,21 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>latex 260 largo figuras perrito payaso globoflexia</t>
-        </is>
-      </c>
+          <t>latex cromado cromo espejo lujo</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-confeti-12-10</t>
+          <t>globo-latex-5-mini-100</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Globo transparente con confeti 12", bolsa 10 pzas</t>
+          <t>Globo de látex 5" mini, bolsa 100 pzas</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2877,39 +3462,39 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Bodas y aniversarios, XV años, Baby shower</t>
+          <t>Baby shower, Cumpleaños, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>bolsa con 100 piezas</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Globo transparente que ya trae confeti metálico dentro. Al inflarlo y frotarlo, el confeti se pega a las paredes.</t>
+          <t>Globito de 5 pulgadas para dar textura a arcos orgánicos, rellenar burbujas y decorar mesas.</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 10 globos con confeti incluido</t>
+          <t>Medida: 5 in (13 cm) inflado; Contenido: 100 piezas; Material: Látex natural</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Oro rosa, Rosa, Azul</t>
+          <t>Rosa, Rojo, Azul rey, Verde limón, Lila, Amarillo, Blanco, Negro</t>
         </is>
       </c>
       <c r="M26" s="3" t="n"/>
@@ -2923,7 +3508,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -2933,19 +3518,21 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>latex confeti transparente brillos</t>
-        </is>
-      </c>
+          <t>latex mini 5 pulgadas chico arco organico relleno</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-corazon-12-50</t>
+          <t>globo-latex-18-10</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex corazón 12", bolsa 50 pzas</t>
+          <t>Globo de látex 18", bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2955,39 +3542,39 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Amor y amistad, Bodas y aniversarios, XV años</t>
+          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Globos de látex en forma de corazón para San Valentín, bodas y declaraciones.</t>
+          <t>Globo grande de 18 pulgadas para dar volumen en arcos y columnas.</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas</t>
+          <t>Medida: 18 in (45 cm) inflado; Contenido: 10 piezas; Material: Látex natural</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Fucsia, Blanco</t>
+          <t>Azul cielo, Rosa, Rojo, Amarillo, Blanco, Negro</t>
         </is>
       </c>
       <c r="M27" s="3" t="n"/>
@@ -3011,19 +3598,21 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>latex corazon corazones amor san valentin</t>
-        </is>
-      </c>
+          <t>latex 18 pulgadas grande arco columna</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-feliz-cumple-12-50</t>
+          <t>globo-latex-260-50</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex impreso "Feliz Cumple", bolsa 50 pzas</t>
+          <t>Globo de látex 260 para figuras, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3033,14 +3622,14 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles</t>
+          <t>Fiestas infantiles, Cumpleaños</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>6</v>
@@ -3051,19 +3640,23 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Globos de 12 pulgadas en colores surtidos con "Feliz Cumpleaños" impreso alrededor.</t>
+          <t>Globo largo para hacer perritos, espadas, flores y figuras. Se infla con inflador manual.</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas en colores surtidos; Impresión: A una tinta, todo alrededor</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="n"/>
+          <t>Medida: 5 × 150 cm inflado (260Q); Contenido: 50 piezas; Inflado: Con inflador manual</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Surtido, Blanco, Rojo, Azul, Verde, Amarillo, Negro</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="n"/>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="n"/>
@@ -3085,19 +3678,21 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>latex impreso feliz cumpleaños cumple surtido</t>
-        </is>
-      </c>
+          <t>latex 260 largo figuras perrito payaso globoflexia</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-36-gigante</t>
+          <t>globo-latex-confeti-12-10</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex gigante 36"</t>
+          <t>Globo transparente con confeti 12", bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3107,39 +3702,39 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Revelación de género, Bodas y aniversarios</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Baby shower</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Globo de 3 pies (90 cm) para fotos, revelaciones de género y como pieza central de una decoración.</t>
+          <t>Globo transparente que ya trae confeti metálico dentro. Al inflarlo y frotarlo, el confeti se pega a las paredes.</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Medida: 36 in (90 cm) inflado; Material: Látex natural grueso</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 10 globos con confeti incluido</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Rosa, Rojo, Azul cielo, Dorado, Blanco, Negro</t>
+          <t>Dorado, Plateado, Oro rosa, Rosa, Azul</t>
         </is>
       </c>
       <c r="M29" s="3" t="n"/>
@@ -3153,7 +3748,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3163,19 +3758,21 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>latex gigante 36 jumbo grande revelacion</t>
-        </is>
-      </c>
+          <t>latex confeti transparente brillos</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>kit-arco-organico</t>
+          <t>globo-latex-corazon-12-50</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Kit arco orgánico de globos (100 pzas)</t>
+          <t>Globo de látex corazón 12", bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3185,57 +3782,53 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Cumpleaños, Bodas y aniversarios, XV años, Revelación de género</t>
+          <t>Amor y amistad, Bodas y aniversarios, XV años</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Todo para armar un arco orgánico de 2.5 a 3 metros: 100 globos en tres tamaños, cinta para arco y puntos de pegamento.</t>
+          <t>Globos de látex en forma de corazón para San Valentín, bodas y declaraciones.</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Incluye: 100 globos (5", 10" y 12"), 5 m de cinta y 1 rollo de puntos de pegamento; Largo aproximado: 2.5 a 3 m</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>Paleta</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Rosa y dorado, Azul y plata, Pastel arcoíris, Salvia y blanco, Negro y dorado</t>
-        </is>
-      </c>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Fucsia, Blanco</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="n"/>
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -3245,19 +3838,21 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>kit arco organico guirnalda decoracion set</t>
-        </is>
-      </c>
+          <t>latex corazon corazones amor san valentin</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>inflador-manual-doble-accion</t>
+          <t>globo-latex-feliz-cumple-12-50</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Inflador manual de doble acción</t>
+          <t>Globo de látex impreso "Feliz Cumple", bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -3265,39 +3860,39 @@
           <t>Globos de látex</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Fiestas infantiles</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Infla al subir y al bajar, así terminas el doble de rápido. Sirve para látex, globos 260 y foil con aire.</t>
+          <t>Globos de 12 pulgadas en colores surtidos con "Feliz Cumpleaños" impreso alrededor.</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Largo: 30 cm; Uso: Látex, 260 y foil chico; Incluye: Boquilla para globo 260</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>Azul, Rosa, Morado</t>
-        </is>
-      </c>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas en colores surtidos; Impresión: A una tinta, todo alrededor</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="n"/>
@@ -3319,19 +3914,21 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>inflador bomba accesorio herramienta</t>
-        </is>
-      </c>
+          <t>latex impreso feliz cumpleaños cumple surtido</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="n"/>
+      <c r="V31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>cinta-para-arco-5m</t>
+          <t>globo-latex-36-gigante</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cinta para arco de globos, 5 m</t>
+          <t>Globo de látex gigante 36"</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3339,35 +3936,43 @@
           <t>Globos de látex</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Baby shower, Revelación de género, Bodas y aniversarios</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>rollo de 5 m</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Tira de plástico con orificios para insertar los nudos de los globos y armar arcos y guirnaldas sin pegamento.</t>
+          <t>Globo de 3 pies (90 cm) para fotos, revelaciones de género y como pieza central de una decoración.</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Largo: 5 m; Material: PVC transparente</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="n"/>
+          <t>Medida: 36 in (90 cm) inflado; Material: Látex natural grueso</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Rosa, Rojo, Azul cielo, Dorado, Blanco, Negro</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="n"/>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="n"/>
@@ -3389,65 +3994,71 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>cinta arco tira accesorio guirnalda</t>
-        </is>
-      </c>
+          <t>latex gigante 36 jumbo grande revelacion</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>papel-china-50-pliegos</t>
+          <t>kit-arco-organico</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Papel china, paquete 50 pliegos</t>
+          <t>Kit arco orgánico de globos (100 pzas)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
+          <t>Globos de látex</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Fiestas patrias, Navidad, Cumpleaños, Fiestas infantiles</t>
+          <t>Baby shower, Cumpleaños, Bodas y aniversarios, XV años, Revelación de género</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>55</v>
+        <v>235</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>paquete con 50 pliegos</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Papel de china para piñatas, papel picado, flores, borlas y manualidades. Paquete de 50 pliegos de un solo color.</t>
+          <t>Todo para armar un arco orgánico de 2.5 a 3 metros: 100 globos en tres tamaños, cinta para arco y puntos de pegamento.</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Medida del pliego: 50 × 75 cm; Contenido: 50 pliegos</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>Rosa, Fucsia, Rojo, Naranja, Amarillo, Verde bandera, Verde limón, Azul cielo, Azul rey, Morado, Blanco, Negro</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
+          <t>Incluye: 100 globos (5", 10" y 12"), 5 m de cinta y 1 rollo de puntos de pegamento; Largo aproximado: 2.5 a 3 m</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Paleta</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Rosa y dorado, Azul y plata, Pastel arcoíris, Salvia y blanco, Negro y dorado</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="n"/>
       <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="inlineStr">
@@ -3457,7 +4068,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -3467,61 +4078,59 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>papel china piñata manualidades pliegos</t>
-        </is>
-      </c>
+          <t>kit arco organico guirnalda decoracion set</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>papel-crepe-pliego</t>
+          <t>inflador-manual-doble-accion</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Papel crepé, pliego 50 × 200 cm</t>
+          <t>Inflador manual de doble acción</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Fiestas infantiles, Fiestas patrias, Navidad</t>
-        </is>
-      </c>
+          <t>Globos de látex</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="4" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Papel crepé elástico para flores, disfraces, cortinas y forrar mesas.</t>
+          <t>Infla al subir y al bajar, así terminas el doble de rápido. Sirve para látex, globos 260 y foil con aire.</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 200 cm; Textura: Corrugado elástico</t>
+          <t>Largo: 30 cm; Uso: Látex, 260 y foil chico; Incluye: Boquilla para globo 260</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro</t>
+          <t>Azul, Rosa, Morado</t>
         </is>
       </c>
       <c r="M34" s="3" t="n"/>
@@ -3545,59 +4154,57 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>papel crepe crepé flores disfraz manualidades</t>
-        </is>
-      </c>
+          <t>inflador bomba accesorio herramienta</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="n"/>
+      <c r="V34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>cartulina-pliego</t>
+          <t>cinta-para-arco-5m</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Cartulina, pliego 50 × 65 cm</t>
+          <t>Cinta para arco de globos, 5 m</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
+          <t>Globos de látex</t>
         </is>
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>rollo de 5 m</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Cartulina de colores para letreros, carteles, tareas y manualidades.</t>
+          <t>Tira de plástico con orificios para insertar los nudos de los globos y armar arcos y guirnaldas sin pegamento.</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 65 cm; Gramaje: 180 g/m² aprox.</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>Amarillo, Rosa, Rojo, Verde, Azul cielo, Azul rey, Naranja, Morado, Blanco, Negro</t>
-        </is>
-      </c>
+          <t>Largo: 5 m; Material: PVC transparente</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="n"/>
@@ -3619,19 +4226,21 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>cartulina carteles letrero escolar</t>
-        </is>
-      </c>
+          <t>cinta arco tira accesorio guirnalda</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="n"/>
+      <c r="V35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>papel-picado-plastico-5m</t>
+          <t>papel-china-50-pliegos</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Papel picado de plástico, tira 5 m</t>
+          <t>Papel china, paquete 50 pliegos</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3641,47 +4250,43 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Fiestas patrias, Bodas y aniversarios, XV años, Cumpleaños</t>
+          <t>Fiestas patrias, Navidad, Cumpleaños, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>tira de 5 m</t>
+          <t>paquete con 50 pliegos</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Papel picado de plástico resistente al aire y la lluvia, para posadas, patios y salones. Tira de 5 metros con 10 pliegos.</t>
+          <t>Papel de china para piñatas, papel picado, flores, borlas y manualidades. Paquete de 50 pliegos de un solo color.</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Largo: 5 m con 10 pliegos; Material: Plástico, se puede reusar</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Multicolor, Navidad, Tricolor, Blanco y dorado</t>
-        </is>
-      </c>
+          <t>Medida del pliego: 50 × 75 cm; Contenido: 50 pliegos</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Rosa, Fucsia, Rojo, Naranja, Amarillo, Verde bandera, Verde limón, Azul cielo, Azul rey, Morado, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n"/>
       <c r="P36" s="3" t="n"/>
       <c r="Q36" s="3" t="inlineStr">
@@ -3701,19 +4306,21 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>papel picado plastico posada navidad fiestas patrias</t>
-        </is>
-      </c>
+          <t>papel china piñata manualidades pliegos</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>banderin-feliz-cumpleanos</t>
+          <t>papel-crepe-pliego</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Banderín "Feliz Cumpleaños", 2.5 m</t>
+          <t>Papel crepé, pliego 50 × 200 cm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3723,47 +4330,43 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles</t>
+          <t>Fiestas infantiles, Fiestas patrias, Navidad</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Guirnalda de banderines con la frase "Feliz Cumpleaños", ya armada con cordón.</t>
+          <t>Papel crepé elástico para flores, disfraces, cortinas y forrar mesas.</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Largo: 2.5 m; Material: Cartulina gruesa</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Multicolor, Rosa, Azul</t>
-        </is>
-      </c>
+          <t>Medida: 50 × 200 cm; Textura: Corrugado elástico</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n"/>
       <c r="P37" s="3" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
@@ -3783,19 +4386,21 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>banderin guirnalda letrero feliz cumpleaños</t>
-        </is>
-      </c>
+          <t>papel crepe crepé flores disfraz manualidades</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>invitaciones-paquete-10</t>
+          <t>cartulina-pliego</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Invitaciones con sobre, paquete 10</t>
+          <t>Cartulina, pliego 50 × 65 cm</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3803,49 +4408,41 @@
           <t>Papelería</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, XV años, Bodas y aniversarios</t>
-        </is>
-      </c>
+      <c r="D38" s="3" t="n"/>
       <c r="E38" s="4" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>paquete con 10 invitaciones</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Invitaciones impresas para llenar a mano, con sobre. Elige el diseño de tu evento.</t>
+          <t>Cartulina de colores para letreros, carteles, tareas y manualidades.</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Medida: 10 × 15 cm; Contenido: 10 invitaciones y 10 sobres</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños infantil, Baby shower, XV años, Boda</t>
-        </is>
-      </c>
+          <t>Medida: 50 × 65 cm; Gramaje: 180 g/m² aprox.</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Amarillo, Rosa, Rojo, Verde, Azul cielo, Azul rey, Naranja, Morado, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="n"/>
       <c r="P38" s="3" t="n"/>
       <c r="Q38" s="3" t="inlineStr">
@@ -3865,19 +4462,21 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>invitaciones invitacion sobre tarjetas</t>
-        </is>
-      </c>
+          <t>cartulina carteles letrero escolar</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n"/>
+      <c r="V38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>foami-carta-10</t>
+          <t>papel-picado-plastico-5m</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Foami tamaño carta, paquete 10 hojas</t>
+          <t>Papel picado de plástico, tira 5 m</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3887,55 +4486,59 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Fiestas infantiles</t>
+          <t>Navidad, Fiestas patrias, Bodas y aniversarios, XV años, Cumpleaños</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>paquete con 10 hojas</t>
+          <t>tira de 5 m</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Hojas de foami de 2 mm para manualidades, letreros y decoración escolar.</t>
+          <t>Papel picado de plástico resistente al aire y la lluvia, para posadas, patios y salones. Tira de 5 metros con 10 pliegos.</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Medida: Carta (21.5 × 28 cm); Grosor: 2 mm; Contenido: 10 hojas</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro, Café</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
+          <t>Largo: 5 m con 10 pliegos; Material: Plástico, se puede reusar</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Multicolor, Navidad, Tricolor, Blanco y dorado</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -3943,19 +4546,21 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>foami fomi goma eva manualidades escolar</t>
-        </is>
-      </c>
+          <t>papel picado plastico posada navidad fiestas patrias</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>foami-diamantado-carta-5</t>
+          <t>banderin-feliz-cumpleanos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Foami diamantado carta, paquete 5 hojas</t>
+          <t>Banderín "Feliz Cumpleaños", 2.5 m</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3965,43 +4570,47 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>XV años, Navidad, Fiestas infantiles</t>
+          <t>Cumpleaños, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>40</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>paquete con 5 hojas</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Foami con brillantina que no se cae. Para coronas, letreros y adornos con brillo.</t>
+          <t>Guirnalda de banderines con la frase "Feliz Cumpleaños", ya armada con cordón.</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Medida: Carta (21.5 × 28 cm); Contenido: 5 hojas</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rosa, Rojo, Azul, Morado, Verde</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+          <t>Largo: 2.5 m; Material: Cartulina gruesa</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Multicolor, Rosa, Azul</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="inlineStr">
@@ -4021,19 +4630,21 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>foami diamantado brillantina glitter escarchado</t>
-        </is>
-      </c>
+          <t>banderin guirnalda letrero feliz cumpleaños</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="n"/>
+      <c r="V40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>papel-metalico-pliego</t>
+          <t>invitaciones-paquete-10</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Papel metálico, pliego 50 × 70 cm</t>
+          <t>Invitaciones con sobre, paquete 10</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4043,43 +4654,47 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Graduación</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, XV años, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>paquete con 10 invitaciones</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Papel con acabado espejo para forrar cajas, hacer moños y decorar fondos.</t>
+          <t>Invitaciones impresas para llenar a mano, con sobre. Elige el diseño de tu evento.</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 70 cm; Acabado: Metálico brillante</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+          <t>Medida: 10 × 15 cm; Contenido: 10 invitaciones y 10 sobres</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños infantil, Baby shower, XV años, Boda</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="n"/>
       <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
@@ -4099,19 +4714,21 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>papel metalico espejo lustre brillante</t>
-        </is>
-      </c>
+          <t>invitaciones invitacion sobre tarjetas</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="n"/>
+      <c r="V41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>topper-feliz-cumple</t>
+          <t>foami-carta-10</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Topper para pastel "Feliz Cumple"</t>
+          <t>Foami tamaño carta, paquete 10 hojas</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -4121,39 +4738,39 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños</t>
+          <t>Fiestas infantiles</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>paquete con 10 hojas</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Adorno para pastel de cartulina metálica, con palitos para insertar.</t>
+          <t>Hojas de foami de 2 mm para manualidades, letreros y decoración escolar.</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Medida: 15 × 12 cm; Material: Cartulina metálica</t>
+          <t>Medida: Carta (21.5 × 28 cm); Grosor: 2 mm; Contenido: 10 hojas</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Oro rosa, Negro</t>
+          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro, Café</t>
         </is>
       </c>
       <c r="M42" s="3" t="n"/>
@@ -4177,74 +4794,72 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>topper pastel adorno cake</t>
-        </is>
-      </c>
+          <t>foami fomi goma eva manualidades escolar</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="n"/>
+      <c r="V42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>papel-envolver-rollo-5m</t>
+          <t>foami-diamantado-carta-5</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Papel para envolver, rollo 70 cm × 5 m</t>
+          <t>Foami diamantado carta, paquete 5 hojas</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>XV años, Navidad, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>paquete con 5 hojas</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Papel para regalo en rollo con tubo de cartón. Alcanza para envolver de 8 a 10 regalos medianos.</t>
+          <t>Foami con brillantina que no se cae. Para coronas, letreros y adornos con brillo.</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Medida: 70 cm × 5 m; Papel: Couché 60 g/m²</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Medida: Carta (21.5 × 28 cm); Contenido: 5 hojas</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rosa, Rojo, Azul, Morado, Verde</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n"/>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
@@ -4259,69 +4874,67 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>papel envolver regalo rollo envoltura</t>
-        </is>
-      </c>
+          <t>foami diamantado brillantina glitter escarchado</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>papel-envolver-pliegos-25</t>
+          <t>papel-metalico-pliego</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Papel para envolver, paquete 25 pliegos</t>
+          <t>Papel metálico, pliego 50 × 70 cm</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Navidad, Graduación</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>paquete con 25 pliegos</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Pliegos para regalo del mismo diseño, ideales para tiendas y mesas de regalos.</t>
+          <t>Papel con acabado espejo para forrar cajas, hacer moños y decorar fondos.</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Medida del pliego: 70 × 100 cm; Contenido: 25 pliegos</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Medida: 50 × 70 cm; Acabado: Metálico brillante</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n"/>
       <c r="Q44" s="3" t="inlineStr">
@@ -4341,59 +4954,65 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>papel envolver regalo pliegos mayoreo</t>
-        </is>
-      </c>
+          <t>papel metalico espejo lustre brillante</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>papel-kraft-rollo-10m</t>
+          <t>topper-feliz-cumple</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Papel kraft, rollo 90 cm × 10 m</t>
+          <t>Topper para pastel "Feliz Cumple"</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, Navidad</t>
+          <t>Cumpleaños</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1100</v>
+        <v>15</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Papel kraft natural para envolturas rústicas, manteles de mesa de postres y empaques.</t>
+          <t>Adorno para pastel de cartulina metálica, con palitos para insertar.</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Medida: 90 cm × 10 m; Gramaje: 80 g/m²</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
+          <t>Medida: 15 × 12 cm; Material: Cartulina metálica</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Oro rosa, Negro</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="n"/>
@@ -4415,19 +5034,21 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>papel kraft estraza rustico empaque</t>
-        </is>
-      </c>
+          <t>topper pastel adorno cake</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n"/>
+      <c r="V45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>mono-grande-bolsa-10</t>
+          <t>papel-envolver-rollo-5m</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Moño grande para regalo, bolsa 10 pzas</t>
+          <t>Papel para envolver, rollo 70 cm × 5 m</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4437,55 +5058,59 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad, Bodas y aniversarios, Amor y amistad</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>rollo</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Moños de listón satinado ya armados, con adhesivo en la base.</t>
+          <t>Papel para regalo en rollo con tubo de cartón. Alcanza para envolver de 8 a 10 regalos medianos.</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Diámetro: 12 cm; Contenido: 10 moños del mismo color</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Dorado, Plateado, Azul, Morado, Blanco, Verde</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
+          <t>Medida: 70 cm × 5 m; Papel: Couché 60 g/m²</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -4493,19 +5118,21 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>moño moños regalo listón adhesivo</t>
-        </is>
-      </c>
+          <t>papel envolver regalo rollo envoltura</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>mono-estrella-bolsa-50</t>
+          <t>papel-envolver-pliegos-25</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Moño estrella chico, bolsa 50 pzas</t>
+          <t>Papel para envolver, paquete 25 pliegos</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4515,43 +5142,47 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Cumpleaños</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>paquete con 25 pliegos</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Moño estrella metálico de 6 cm con adhesivo, para regalos pequeños y bolsas.</t>
+          <t>Pliegos para regalo del mismo diseño, ideales para tiendas y mesas de regalos.</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Diámetro: 6 cm; Contenido: 50 moños</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
+          <t>Medida del pliego: 70 × 100 cm; Contenido: 25 pliegos</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O47" s="3" t="n"/>
       <c r="P47" s="3" t="n"/>
       <c r="Q47" s="3" t="inlineStr">
@@ -4571,19 +5202,21 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>moño estrella chico regalo metalico</t>
-        </is>
-      </c>
+          <t>papel envolver regalo pliegos mayoreo</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="n"/>
+      <c r="V47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>liston-satinado-1in-20m</t>
+          <t>papel-kraft-rollo-10m</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Listón satinado 1", rollo 20 m</t>
+          <t>Papel kraft, rollo 90 cm × 10 m</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4593,41 +5226,37 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Navidad, Amor y amistad</t>
+          <t>Bodas y aniversarios, Navidad</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>rollo de 20 m</t>
+          <t>rollo</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>75</v>
+        <v>1100</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Listón satinado de doble cara para moños, recuerdos, arreglos florales y envolturas.</t>
+          <t>Papel kraft natural para envolturas rústicas, manteles de mesa de postres y empaques.</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Ancho: 1 in (2.5 cm); Largo: 20 m</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Fucsia, Dorado, Plateado, Azul rey, Azul cielo, Verde, Blanco, Negro, Morado, Vino</t>
-        </is>
-      </c>
+          <t>Medida: 90 cm × 10 m; Gramaje: 80 g/m²</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
       <c r="N48" s="3" t="n"/>
       <c r="O48" s="3" t="n"/>
@@ -4649,19 +5278,21 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>liston satinado moño cinta recuerdos</t>
-        </is>
-      </c>
+          <t>papel kraft estraza rustico empaque</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="n"/>
+      <c r="V48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>liston-rizar-100m</t>
+          <t>mono-grande-bolsa-10</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Listón para rizar, rollo 100 m</t>
+          <t>Moño grande para regalo, bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4671,39 +5302,39 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad</t>
+          <t>Cumpleaños, Navidad, Bodas y aniversarios, Amor y amistad</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>rollo de 100 m</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Listón de rafia que se riza con tijera. Sirve para amarrar globos y decorar regalos.</t>
+          <t>Moños de listón satinado ya armados, con adhesivo en la base.</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Ancho: 3/16 in (5 mm); Largo: 100 m</t>
+          <t>Diámetro: 12 cm; Contenido: 10 moños del mismo color</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Dorado, Plateado, Azul, Verde, Morado, Blanco</t>
+          <t>Rojo, Rosa, Dorado, Plateado, Azul, Morado, Blanco, Verde</t>
         </is>
       </c>
       <c r="M49" s="3" t="n"/>
@@ -4727,19 +5358,21 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>liston rizar rafia globos amarrar</t>
-        </is>
-      </c>
+          <t>moño moños regalo listón adhesivo</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="n"/>
+      <c r="V49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>bolsa-regalo-mediana</t>
+          <t>mono-estrella-bolsa-50</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de regalo mediana 26 × 32 cm</t>
+          <t>Moño estrella chico, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4749,52 +5382,48 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Navidad, Cumpleaños</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Bolsa de papel con asas de cordón y refuerzo en la base.</t>
+          <t>Moño estrella metálico de 6 cm con adhesivo, para regalos pequeños y bolsas.</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Medida: 26 × 32 × 12 cm; Asas: Cordón</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="n"/>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Diámetro: 6 cm; Contenido: 50 moños</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
       <c r="O50" s="3" t="n"/>
       <c r="P50" s="3" t="n"/>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
@@ -4809,19 +5438,21 @@
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>bolsa regalo mediana asas</t>
-        </is>
-      </c>
+          <t>moño estrella chico regalo metalico</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="n"/>
+      <c r="V50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>bolsa-regalo-grande</t>
+          <t>liston-satinado-1in-20m</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de regalo grande 33 × 45 cm</t>
+          <t>Listón satinado 1", rollo 20 m</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -4831,47 +5462,43 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Bodas y aniversarios, XV años, Navidad, Amor y amistad</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>rollo de 20 m</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Bolsa grande para peluches, ropa y regalos voluminosos.</t>
+          <t>Listón satinado de doble cara para moños, recuerdos, arreglos florales y envolturas.</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Medida: 33 × 45 × 15 cm; Asas: Cordón</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Ancho: 1 in (2.5 cm); Largo: 20 m</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Fucsia, Dorado, Plateado, Azul rey, Azul cielo, Verde, Blanco, Negro, Morado, Vino</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
       <c r="O51" s="3" t="n"/>
       <c r="P51" s="3" t="n"/>
       <c r="Q51" s="3" t="inlineStr">
@@ -4891,19 +5518,21 @@
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>bolsa regalo grande asas peluche</t>
-        </is>
-      </c>
+          <t>liston satinado moño cinta recuerdos</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="n"/>
+      <c r="V51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>bolsa-celofan-15x25-100</t>
+          <t>liston-rizar-100m</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de celofán 15 × 25 cm, paquete 100</t>
+          <t>Listón para rizar, rollo 100 m</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -4913,37 +5542,41 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Navidad</t>
+          <t>Cumpleaños, Navidad</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>paquete con 100 bolsas</t>
+          <t>rollo de 100 m</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Bolsitas transparentes para dulceros, aguinaldos de posada, galletas y recuerdos.</t>
+          <t>Listón de rafia que se riza con tijera. Sirve para amarrar globos y decorar regalos.</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Medida: 15 × 25 cm; Contenido: 100 bolsas</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="n"/>
+          <t>Ancho: 3/16 in (5 mm); Largo: 100 m</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Dorado, Plateado, Azul, Verde, Morado, Blanco</t>
+        </is>
+      </c>
       <c r="M52" s="3" t="n"/>
       <c r="N52" s="3" t="n"/>
       <c r="O52" s="3" t="n"/>
@@ -4965,19 +5598,21 @@
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>bolsa celofan dulcero dulces aguinaldo posada galletas recuerdos</t>
-        </is>
-      </c>
+          <t>liston rizar rafia globos amarrar</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="n"/>
+      <c r="V52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>celofan-rollo-1x20m</t>
+          <t>bolsa-regalo-mediana</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Papel celofán, rollo 1 × 20 m</t>
+          <t>Bolsa de regalo mediana 26 × 32 cm</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4987,55 +5622,59 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Amor y amistad</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Celofán para envolver canastas, arcones, arreglos y ramos.</t>
+          <t>Bolsa de papel con asas de cordón y refuerzo en la base.</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Medida: 1 × 20 m; Calibre: Grueso, no se rompe al doblar</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>Transparente, Rojo #e63946, Rosa, Azul, Verde</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
+          <t>Medida: 26 × 32 × 12 cm; Asas: Cordón</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O53" s="3" t="n"/>
       <c r="P53" s="3" t="n"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -5043,19 +5682,21 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>celofan rollo canasta arcon arreglo transparente</t>
-        </is>
-      </c>
+          <t>bolsa regalo mediana asas</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="n"/>
+      <c r="V53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>caja-regalo-set-3</t>
+          <t>bolsa-regalo-grande</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Cajas de regalo con tapa, set de 3</t>
+          <t>Bolsa de regalo grande 33 × 45 cm</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -5065,43 +5706,47 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>set de 3 cajas</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>650</v>
+        <v>120</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Tres cajas rígidas con tapa que se guardan una dentro de otra. Incluyen listón decorativo.</t>
+          <t>Bolsa grande para peluches, ropa y regalos voluminosos.</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Medidas: 25 × 25, 20 × 20 y 15 × 15 cm; Material: Cartón rígido forrado</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Kraft, Blanco, Rosa, Negro, Azul rey</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
+          <t>Medida: 33 × 45 × 15 cm; Asas: Cordón</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="n"/>
       <c r="P54" s="3" t="n"/>
       <c r="Q54" s="3" t="inlineStr">
@@ -5121,19 +5766,21 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>caja cajas regalo tapa set</t>
-        </is>
-      </c>
+          <t>bolsa regalo grande asas peluche</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="n"/>
+      <c r="V54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>papel-seda-24-hojas</t>
+          <t>bolsa-celofan-15x25-100</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Papel seda para regalo, paquete 24 hojas</t>
+          <t>Bolsa de celofán 15 × 25 cm, paquete 100</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5143,41 +5790,37 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Navidad</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>paquete con 24 hojas</t>
+          <t>paquete con 100 bolsas</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Papel seda delgado para acomodar dentro de bolsas y cajas de regalo.</t>
+          <t>Bolsitas transparentes para dulceros, aguinaldos de posada, galletas y recuerdos.</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 70 cm; Contenido: 24 hojas</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>Rosa pastel, Rosa, Rojo, Dorado, Azul cielo, Lila, Blanco, Negro</t>
-        </is>
-      </c>
+          <t>Medida: 15 × 25 cm; Contenido: 100 bolsas</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n"/>
       <c r="M55" s="3" t="n"/>
       <c r="N55" s="3" t="n"/>
       <c r="O55" s="3" t="n"/>
@@ -5199,19 +5842,21 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>papel seda tissue relleno bolsa regalo</t>
-        </is>
-      </c>
+          <t>bolsa celofan dulcero dulces aguinaldo posada galletas recuerdos</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="n"/>
+      <c r="V55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>relleno-viruta-papel-100g</t>
+          <t>celofan-rollo-1x20m</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Relleno de viruta de papel, 100 g</t>
+          <t>Papel celofán, rollo 1 × 20 m</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -5221,39 +5866,39 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Navidad, Amor y amistad</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>bolsa de 100 g</t>
+          <t>rollo</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Papel triturado para canastas, cajas de regalo y arcones navideños.</t>
+          <t>Celofán para envolver canastas, arcones, arreglos y ramos.</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Contenido: 100 g; Material: Papel reciclado</t>
+          <t>Medida: 1 × 20 m; Calibre: Grueso, no se rompe al doblar</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Kraft, Blanco, Rosa, Rojo, Dorado, Negro, Verde, Azul</t>
+          <t>Transparente, Rojo #e63946, Rosa, Azul, Verde</t>
         </is>
       </c>
       <c r="M56" s="3" t="n"/>
@@ -5277,12 +5922,254 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
+          <t>celofan rollo canasta arcon arreglo transparente</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n"/>
+      <c r="V56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>caja-regalo-set-3</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Cajas de regalo con tapa, set de 3</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Navidad, Amor y amistad, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>set de 3 cajas</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Tres cajas rígidas con tapa que se guardan una dentro de otra. Incluyen listón decorativo.</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Medidas: 25 × 25, 20 × 20 y 15 × 15 cm; Material: Cartón rígido forrado</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Kraft, Blanco, Rosa, Negro, Azul rey</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>caja cajas regalo tapa set</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n"/>
+      <c r="V57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>papel-seda-24-hojas</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Papel seda para regalo, paquete 24 hojas</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>paquete con 24 hojas</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Papel seda delgado para acomodar dentro de bolsas y cajas de regalo.</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Medida: 50 × 70 cm; Contenido: 24 hojas</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Rosa pastel, Rosa, Rojo, Dorado, Azul cielo, Lila, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="3" t="n"/>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>papel seda tissue relleno bolsa regalo</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="n"/>
+      <c r="V58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>relleno-viruta-papel-100g</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Relleno de viruta de papel, 100 g</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Navidad, Amor y amistad, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>bolsa de 100 g</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Papel triturado para canastas, cajas de regalo y arcones navideños.</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Contenido: 100 g; Material: Papel reciclado</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Kraft, Blanco, Rosa, Rojo, Dorado, Negro, Verde, Azul</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="3" t="n"/>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
           <t>viruta relleno papel triturado canasta arcon</t>
         </is>
       </c>
+      <c r="U59" s="3" t="n"/>
+      <c r="V59" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56"/>
+  <autoFilter ref="A1:V59"/>
   <dataValidations count="8">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una de las categorías de la lista." type="list">
       <formula1>"Globos de foil,Globos de látex,Papelería,Envolturas"</formula1>
@@ -5320,7 +6207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D50"/>
+  <dimension ref="B1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5478,404 +6365,473 @@
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Fotos</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+          <t>Tamaños y carta de colores (Sempertex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>• Crea en Google Drive una carpeta "Fotos tienda" y súbelas ahí. De preferencia cuadradas, de unos 800 × 800 px.</t>
+          <t>• Un producto con varios tamaños lleva una fila por tamaño, todas con el MISMO nombre, y en "Presentación" el tamaño (5", 12", 18"). Cada fila tiene su precio, mayoreo, peso y "Se vende por".</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>• Comparte la carpeta como "Cualquier persona con el enlace". Luego, en cada foto: clic derecho → Compartir → Copiar enlace, y pégalo en la columna Foto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>• En "Colores" escribe "Carta Sempertex" para poner los 85 tonos, "Sempertex Reflex" para una sola familia, o códigos sueltos como "015, 041, 970". La pestaña "Carta Sempertex" tiene todos los códigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>• Para una foto distinta por color usa la columna "Fotos por opción":  Dorado = enlace; Plateado = enlace</t>
+          <t>• En "Colores agotados" escribe los códigos que no tienes, por ejemplo "015, 390". Si lo pones solo en la fila de 18", ese tono se ve tachado solo en 18".</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>• Si un producto no tiene foto, la tienda muestra una ilustración con la leyenda "Imagen ilustrativa".</t>
+          <t>• Si un tamaño se acabó, pon Estado = Agotado en su fila: los otros tamaños se siguen vendiendo.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="8" t="inlineStr">
         <is>
+          <t>Fotos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>• Crea en Google Drive una carpeta "Fotos tienda" y súbelas ahí. De preferencia cuadradas, de unos 800 × 800 px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>• Comparte la carpeta como "Cualquier persona con el enlace". Luego, en cada foto: clic derecho → Compartir → Copiar enlace, y pégalo en la columna Foto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>• Para una foto distinta por color usa la columna "Fotos por opción":  Dorado = enlace; Plateado = enlace</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>• Si un producto no tiene foto, la tienda muestra una ilustración con la leyenda "Imagen ilustrativa".</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>Qué va en cada columna</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Columna</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Qué poner</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Ejemplo</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="12" t="inlineStr">
+    <row r="37" ht="45" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos.</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>globo-foil-estrella-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Obligatorio. Nombre que ven los clientes.</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Globo foil estrella 18"</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Obligatorio. Una de: Globos de foil, Globos de látex, Papelería, Envolturas.</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Globos de foil</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Temáticas</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Separadas por comas. Si escribes una que no existe (por ejemplo "Día de las Madres"), la tienda la crea sola.</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Navidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Precio</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Obligatorio. Precio de menudeo en pesos, solo el número.</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Precio mayoreo</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Precio por unidad al llegar a la cantidad mínima. Déjalo vacío si no hay mayoreo.</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Mayoreo desde</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Cantidad mínima para el precio de mayoreo. Se suman todos los colores del mismo producto.</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Se vende por</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Cómo se vende. Vacío = "pieza".</t>
+          <t>Obligatorio. Nombre que ven los clientes.</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+          <t>Globo foil estrella 18"</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Peso (g)</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Gramos por unidad vendida. Se usa para calcular el envío; si falta se usan 100 g.</t>
+          <t>Obligatorio. Una de: Globos de foil, Globos de látex, Papelería, Envolturas.</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+          <t>Globos de foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Temáticas</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Texto de la página del producto.</t>
+          <t>Separadas por comas. Si escribes una que no existe (por ejemplo "Día de las Madres"), la tienda la crea sola.</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Estrella metálica de 18 pulgadas…</t>
+          <t>Cumpleaños, Navidad</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Características</t>
+          <t>Precio</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Pares "Dato: valor" separados por punto y coma.</t>
+          <t>Obligatorio. Precio de menudeo en pesos, solo el número.</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Medida: 18 in (45 cm); Material: Foil</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Colores</t>
+          <t>Precio mayoreo</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Nombres separados por comas (ver pestaña Listas). Para otro color agrega su código: "Turquesa #1fb5ad".</t>
+          <t>Precio por unidad al llegar a la cantidad mínima. Déjalo vacío si no hay mayoreo.</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Rosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Otra opción</t>
+          <t>Mayoreo desde</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Otra elección del cliente además del color: Número, Letra, Diseño, Tamaño…</t>
+          <t>Cantidad mínima para el precio de mayoreo. Se suman todos los colores del mismo producto.</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Número</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Valores de la opción</t>
+          <t>Se vende por</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Separados por comas. Puedes usar rangos como 0-9 o A-Z.</t>
+          <t>Cómo se vende. Vacío = "pieza".</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>0-9</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Foto</t>
+          <t>Peso (g)</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Enlace de Google Drive de la foto (compartida como "Cualquier persona con el enlace") o nombre de un archivo de la carpeta img. Vacío = ilustración.</t>
+          <t>Gramos por unidad vendida. Se usa para calcular el envío; si falta se usan 100 g.</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/…/view</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Fotos por opción</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Una foto por color u opción: "Dorado = enlace; Plateado = enlace".</t>
+          <t>Texto de la página del producto.</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Dorado = https://drive.google.com/file/d/…</t>
+          <t>Estrella metálica de 18 pulgadas…</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Destacado</t>
+          <t>Características</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sí para mostrarlo en "Lo más pedido".</t>
+          <t>Pares "Dato: valor" separados por punto y coma.</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
+          <t>Medida: 18 in (45 cm); Material: Foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Colores</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Sí para la etiqueta "Nuevo".</t>
+          <t>Nombres separados por comas (ver pestaña Listas). Para otro color agrega su código: "Turquesa #1fb5ad".</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
+          <t>Dorado, Plateado, Rosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Otra opción</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Visible, Agotado (se ve pero no se puede comprar) u Oculto (no aparece en la tienda).</t>
+          <t>Otra elección del cliente además del color: Número, Letra, Diseño, Tamaño…</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Visible</t>
+          <t>Número</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
+          <t>Valores de la opción</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Separados por comas. Puedes usar rangos como 0-9 o A-Z.</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Enlace de Google Drive de la foto (compartida como "Cualquier persona con el enlace") o nombre de un archivo de la carpeta img. Vacío = ilustración.</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/…/view</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Fotos por opción</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Una foto por color u opción: "Dorado = enlace; Plateado = enlace".</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Dorado = https://drive.google.com/file/d/…</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Destacado</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Sí para mostrarlo en "Lo más pedido".</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Sí para la etiqueta "Nuevo".</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Visible, Agotado (se ve pero no se puede comprar) u Oculto (no aparece en la tienda).</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="B56" s="12" t="inlineStr">
+        <is>
           <t>Palabras para buscar</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Otras palabras con las que los clientes buscan este producto.</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>metalico helio estrellas</t>
         </is>
       </c>
     </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Para vender un producto en varios tamaños: haz una fila por tamaño con el MISMO nombre y escribe aquí el tamaño (5", 12", 18"). Cada fila lleva su precio, mayoreo, peso y presentación; en la tienda se ven como un solo producto con selector de tamaño.</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Colores agotados</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Colores o tonos sin existencia, separados por comas (nombres o códigos de la carta). En un producto con tamaños, aplica solo al tamaño de esa fila.</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>015, 390</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="29">
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B1:D1"/>
@@ -5884,17 +6840,22 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
@@ -6488,4 +7449,2014 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Nombre en inglés</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Muestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E2" s="50" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Rosado</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E3" s="51" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Palo de Rosa</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Rosewood</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Fucsia</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E5" s="53" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Frambuesa</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Raspberry</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Rojo Imperial</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Imperial Red</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E8" s="56" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Merlot</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Merlot</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Amarillo Miel</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Honey Yellow</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Mostaza</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Mustard</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Eucalipto</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Eucalyptus</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Verde Trébol</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Shamrock Green</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Verde Lima</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Lime Green</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Verde Bosque</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E17" s="65" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Turquesa Profundo</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Deep Teal</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Aquamarine</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Azul Caribe</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Caribbean Blue</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E20" s="68" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Royal Blue</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Azul Naval</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Navy Blue</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E23" s="71" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E24" s="72" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Violeta</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E25" s="73" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Orquídea Morada</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Purple Orchid</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E26" s="74" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>059</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Coral Tropical</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Tropical Coral</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Durazno</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Peach Blush</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E28" s="76" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>061</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Naranja</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E29" s="77" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t>062</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Naranja Cobrizo</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Sunset Orange</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E30" s="78" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>White Sand</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E31" s="79" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>073</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Latte</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Latte</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E32" s="80" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>074</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Coffee</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E33" s="81" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E34" s="82" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E35" s="83" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>081</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Gris</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Grey</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E36" s="84" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Transparente</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E37" s="85" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Rosado</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E38" s="86" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E39" s="87" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E40" s="88" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E41" s="89" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E42" s="90" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Durazno Malibú</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Malibu Peach</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E43" s="91" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Melón</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Melon</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Mate</t>
+        </is>
+      </c>
+      <c r="E44" s="92" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Fucsia</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Neón</t>
+        </is>
+      </c>
+      <c r="E45" s="93" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Neón</t>
+        </is>
+      </c>
+      <c r="E46" s="94" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="49" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Neón</t>
+        </is>
+      </c>
+      <c r="E47" s="95" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="49" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Neón</t>
+        </is>
+      </c>
+      <c r="E48" s="96" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="49" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Naranja</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Neón</t>
+        </is>
+      </c>
+      <c r="E49" s="97" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Crema</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Dusk</t>
+        </is>
+      </c>
+      <c r="E50" s="98" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Dusk</t>
+        </is>
+      </c>
+      <c r="E51" s="99" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="49" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Té Verde</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Green Tea</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Dusk</t>
+        </is>
+      </c>
+      <c r="E52" s="100" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Dusk</t>
+        </is>
+      </c>
+      <c r="E53" s="101" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Lavanda</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Pastel Dusk</t>
+        </is>
+      </c>
+      <c r="E54" s="102" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E55" s="103" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="49" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Perla</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Pearl</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E56" s="104" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="49" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Rosado</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E57" s="105" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="49" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E58" s="106" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="49" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E59" s="107" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="49" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E60" s="108" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="49" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Plata</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Satín</t>
+        </is>
+      </c>
+      <c r="E61" s="109" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Blanco Nácar</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Oyster White</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E62" s="110" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="49" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Rosa Primaveral</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Pink Blossom</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E63" s="111" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="49" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Verde Menta</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Cool Mint</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E64" s="112" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="49" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Azul Ártico</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Arctic Blue</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E65" s="113" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="49" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Amatista</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Light Amethyst</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E66" s="114" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Dorado</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Gold Dust</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E67" s="115" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Perla Crema</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Cream Pearl</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+      <c r="E68" s="116" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="49" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Fucsia</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E69" s="117" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="49" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E70" s="118" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="49" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E71" s="119" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="49" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E72" s="120" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="49" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Dorado Rosa</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Rose Gold</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E73" s="121" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="49" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Dorado</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E74" s="122" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="49" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Metálico</t>
+        </is>
+      </c>
+      <c r="E75" s="123" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="49" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Rosado</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E76" s="124" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="49" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Fucsia</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E77" s="125" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="49" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Cristal Rojo</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Crystal Red</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E78" s="126" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="49" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Verde Lima</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Lime Green</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E79" s="127" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="49" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Verde Aurora</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Aurora Green</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E80" s="128" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="49" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E81" s="129" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="49" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>Violeta</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E82" s="130" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="49" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Dorado Rosa</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Rose Gold</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E83" s="131" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="49" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Dorado</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E84" s="132" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="49" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Champaña</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E85" s="133" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="49" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Plata</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Reflex</t>
+        </is>
+      </c>
+      <c r="E86" s="134" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="135" t="inlineStr">
+        <is>
+          <t>Los colores de la muestra son aproximados. En la hoja Productos usa el código (por ejemplo 015) en "Colores" o "Colores agotados".</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/plantilla-productos.xlsx
+++ b/plantilla-productos.xlsx
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3062,13 +3062,13 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>

--- a/plantilla-productos.xlsx
+++ b/plantilla-productos.xlsx
@@ -946,7 +946,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos.
+        <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos. En un producto con varios tamaños, pon el mismo código en todas sus filas.
 Ejemplo: globo-foil-estrella-18</t>
       </text>
     </comment>
@@ -2885,7 +2885,11 @@
       <c r="V18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>globo-sempertex-redondo</t>
+        </is>
+      </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Globo Sempertex redondo</t>
@@ -2965,7 +2969,11 @@
       <c r="V19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>globo-sempertex-redondo</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Globo Sempertex redondo</t>
@@ -3045,7 +3053,11 @@
       <c r="V20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>globo-sempertex-redondo</t>
+        </is>
+      </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Globo Sempertex redondo</t>
@@ -6456,7 +6468,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Código</t>
@@ -6464,7 +6476,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos.</t>
+          <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos. En un producto con varios tamaños, pon el mismo código en todas sus filas.</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">

--- a/plantilla-productos.xlsx
+++ b/plantilla-productos.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carta Sempertex" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$V$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$V$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1369,7 +1369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2916,25 +2916,25 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 100 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen. El acabado espejo está en el Globo Sempertex Reflex.</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 74, en 7 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk y Metálico</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Carta Sempertex</t>
+          <t>Sempertex Fashion, Sempertex Pastel Mate, Sempertex Neón, Sempertex Pastel Dusk, Sempertex Satín, Sempertex Silk, Sempertex Metálico</t>
         </is>
       </c>
       <c r="M19" s="3" t="n"/>
@@ -3008,17 +3008,17 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen. El acabado espejo está en el Globo Sempertex Reflex.</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 74, en 7 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk y Metálico</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Carta Sempertex</t>
+          <t>Sempertex Fashion, Sempertex Pastel Mate, Sempertex Neón, Sempertex Pastel Dusk, Sempertex Satín, Sempertex Silk, Sempertex Metálico</t>
         </is>
       </c>
       <c r="M20" s="3" t="n"/>
@@ -3092,17 +3092,17 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen.</t>
+          <t>Globo redondo de látex Sempertex con colores firmes y acabado parejo. Elige el tono en la carta de colores y el tamaño: 5" para arcos orgánicos y rellenos, 12" para decoración en general y 18" para dar volumen. El acabado espejo está en el Globo Sempertex Reflex.</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 85, en 8 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk, Metálico y Reflex</t>
+          <t>Marca: Sempertex; Forma: Redondo; Material: Látex natural; Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 74, en 7 familias: Fashion, Pastel Mate, Neón, Pastel Dusk, Satín, Silk y Metálico</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Carta Sempertex</t>
+          <t>Sempertex Fashion, Sempertex Pastel Mate, Sempertex Neón, Sempertex Pastel Dusk, Sempertex Satín, Sempertex Silk, Sempertex Metálico</t>
         </is>
       </c>
       <c r="M21" s="3" t="n"/>
@@ -3139,12 +3139,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-12-estandar-50</t>
+          <t>globo-sempertex-reflex-redondo</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" estándar, bolsa 50 pzas</t>
+          <t>Globo Sempertex Reflex redondo</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, Fiestas patrias, Graduación</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -3172,21 +3172,21 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Globo redondo de 12 pulgadas en color sólido, de látex natural. Es el más usado para arcos, columnas y decoración con aire o helio. Cada bolsa trae 50 piezas del mismo color.</t>
+          <t>Globo Sempertex Reflex con efecto espejo, tipo cromo. Brilla como metal y luce en arcos, columnas y decoraciones de lujo. El 18" viene en bolsa de 15 o de 25 piezas.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Material: Látex natural biodegradable; Duración con helio: 8 a 12 horas (más con sellador)</t>
+          <t>Marca: Sempertex; Forma: Redondo; Acabado: Reflex (efecto espejo); Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 11 tonos Reflex</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Fucsia, Lila, Morado, Azul rey, Azul cielo, Verde limón, Amarillo, Naranja, Blanco, Negro</t>
+          <t>Sempertex Reflex</t>
         </is>
       </c>
       <c r="M22" s="3" t="n"/>
@@ -3195,14 +3195,14 @@
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -3210,21 +3210,25 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>latex r12 12 pulgadas bolsa colores arco columna</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="n"/>
+          <t>sempertex reflex cromo espejo metalico latex redondo r5 r12 r18</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>5"</t>
+        </is>
+      </c>
       <c r="V22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-12-pastel-50</t>
+          <t>globo-sempertex-reflex-redondo</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" pastel, bolsa 50 pzas</t>
+          <t>Globo Sempertex Reflex redondo</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3234,17 +3238,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Revelación de género, XV años, Bodas y aniversarios, Fiestas infantiles</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>95</v>
+        <v>314</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>80</v>
+        <v>251.21</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -3252,21 +3256,21 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Tonos pastel tipo macaron para decoraciones suaves: baby shower, bautizos y mesas de postres.</t>
+          <t>Globo Sempertex Reflex con efecto espejo, tipo cromo. Brilla como metal y luce en arcos, columnas y decoraciones de lujo. El 18" viene en bolsa de 15 o de 25 piezas.</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Pastel mate</t>
+          <t>Marca: Sempertex; Forma: Redondo; Acabado: Reflex (efecto espejo); Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 11 tonos Reflex</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Rosa pastel, Lila pastel, Azul pastel, Menta, Amarillo pastel, Durazno</t>
+          <t>Sempertex Reflex</t>
         </is>
       </c>
       <c r="M23" s="3" t="n"/>
@@ -3290,21 +3294,25 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>latex pastel macaron baby bautizo</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n"/>
+          <t>sempertex reflex cromo espejo metalico latex redondo r5 r12 r18</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
       <c r="V23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-12-metalico-50</t>
+          <t>globo-sempertex-reflex-redondo</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 12" metálico perlado, bolsa 50 pzas</t>
+          <t>Globo Sempertex Reflex redondo</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3314,39 +3322,39 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Graduación, Navidad, Cumpleaños</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>110</v>
+        <v>398</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>95</v>
+        <v>318</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 15 piezas</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Acabado perlado con brillo suave. Combina muy bien con globos foil y decoraciones elegantes.</t>
+          <t>Globo Sempertex Reflex con efecto espejo, tipo cromo. Brilla como metal y luce en arcos, columnas y decoraciones de lujo. El 18" viene en bolsa de 15 o de 25 piezas.</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Metálico perlado</t>
+          <t>Marca: Sempertex; Forma: Redondo; Acabado: Reflex (efecto espejo); Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 11 tonos Reflex</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Oro rosa, Azul, Rojo, Rosa, Morado, Verde</t>
+          <t>Sempertex Reflex</t>
         </is>
       </c>
       <c r="M24" s="3" t="n"/>
@@ -3355,14 +3363,14 @@
       <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -3370,21 +3378,25 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>latex metalico perlado brillo</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="n"/>
+          <t>sempertex reflex cromo espejo metalico latex redondo r5 r12 r18</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>18" (15 pz)</t>
+        </is>
+      </c>
       <c r="V24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-12-cromado-25</t>
+          <t>globo-sempertex-reflex-redondo</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex cromado 12", bolsa 25 pzas</t>
+          <t>Globo Sempertex Reflex redondo</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3394,17 +3406,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Graduación, Navidad</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>120</v>
+        <v>687</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>105</v>
+        <v>550</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -3412,21 +3424,21 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Efecto espejo, parecido al foil pero en látex. Para decoraciones de lujo y arcos de evento.</t>
+          <t>Globo Sempertex Reflex con efecto espejo, tipo cromo. Brilla como metal y luce en arcos, columnas y decoraciones de lujo. El 18" viene en bolsa de 15 o de 25 piezas.</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 25 piezas; Acabado: Cromado tipo espejo</t>
+          <t>Marca: Sempertex; Forma: Redondo; Acabado: Reflex (efecto espejo); Tamaños: 5" (13 cm), 12" (30 cm) y 18" (46 cm); Tonos: 11 tonos Reflex</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Oro cromo #c9a227, Plata cromo #a9b1bb, Oro rosa cromo #d9897a, Champagne cromo #d8c08f, Azul cromo #3767c9</t>
+          <t>Sempertex Reflex</t>
         </is>
       </c>
       <c r="M25" s="3" t="n"/>
@@ -3440,7 +3452,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3450,21 +3462,25 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>latex cromado cromo espejo lujo</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n"/>
+          <t>sempertex reflex cromo espejo metalico latex redondo r5 r12 r18</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>18" (25 pz)</t>
+        </is>
+      </c>
       <c r="V25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-5-mini-100</t>
+          <t>globo-latex-12-estandar-50</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 5" mini, bolsa 100 pzas</t>
+          <t>Globo de látex 12" estándar, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3474,39 +3490,39 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Cumpleaños, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Revelación de género, Fiestas patrias, Graduación</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 100 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Globito de 5 pulgadas para dar textura a arcos orgánicos, rellenar burbujas y decorar mesas.</t>
+          <t>Globo redondo de 12 pulgadas en color sólido, de látex natural. Es el más usado para arcos, columnas y decoración con aire o helio. Cada bolsa trae 50 piezas del mismo color.</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Medida: 5 in (13 cm) inflado; Contenido: 100 piezas; Material: Látex natural</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Material: Látex natural biodegradable; Duración con helio: 8 a 12 horas (más con sellador)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Rosa, Rojo, Azul rey, Verde limón, Lila, Amarillo, Blanco, Negro</t>
+          <t>Rojo, Rosa, Fucsia, Lila, Morado, Azul rey, Azul cielo, Verde limón, Amarillo, Naranja, Blanco, Negro</t>
         </is>
       </c>
       <c r="M26" s="3" t="n"/>
@@ -3515,14 +3531,14 @@
       <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -3530,7 +3546,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>latex mini 5 pulgadas chico arco organico relleno</t>
+          <t>latex r12 12 pulgadas bolsa colores arco columna</t>
         </is>
       </c>
       <c r="U26" s="3" t="n"/>
@@ -3539,12 +3555,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-18-10</t>
+          <t>globo-latex-12-pastel-50</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 18", bolsa 10 pzas</t>
+          <t>Globo de látex 12" pastel, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3554,39 +3570,39 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+          <t>Baby shower, Revelación de género, XV años, Bodas y aniversarios, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Globo grande de 18 pulgadas para dar volumen en arcos y columnas.</t>
+          <t>Tonos pastel tipo macaron para decoraciones suaves: baby shower, bautizos y mesas de postres.</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Medida: 18 in (45 cm) inflado; Contenido: 10 piezas; Material: Látex natural</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Pastel mate</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Azul cielo, Rosa, Rojo, Amarillo, Blanco, Negro</t>
+          <t>Rosa pastel, Lila pastel, Azul pastel, Menta, Amarillo pastel, Durazno</t>
         </is>
       </c>
       <c r="M27" s="3" t="n"/>
@@ -3600,7 +3616,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -3610,7 +3626,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>latex 18 pulgadas grande arco columna</t>
+          <t>latex pastel macaron baby bautizo</t>
         </is>
       </c>
       <c r="U27" s="3" t="n"/>
@@ -3619,12 +3635,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-260-50</t>
+          <t>globo-latex-12-metalico-50</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex 260 para figuras, bolsa 50 pzas</t>
+          <t>Globo de látex 12" metálico perlado, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3634,14 +3650,14 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Fiestas infantiles, Cumpleaños</t>
+          <t>Bodas y aniversarios, XV años, Graduación, Navidad, Cumpleaños</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>6</v>
@@ -3652,21 +3668,21 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Globo largo para hacer perritos, espadas, flores y figuras. Se infla con inflador manual.</t>
+          <t>Acabado perlado con brillo suave. Combina muy bien con globos foil y decoraciones elegantes.</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Medida: 5 × 150 cm inflado (260Q); Contenido: 50 piezas; Inflado: Con inflador manual</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas; Acabado: Metálico perlado</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Surtido, Blanco, Rojo, Azul, Verde, Amarillo, Negro</t>
+          <t>Dorado, Plateado, Oro rosa, Azul, Rojo, Rosa, Morado, Verde</t>
         </is>
       </c>
       <c r="M28" s="3" t="n"/>
@@ -3675,14 +3691,14 @@
       <c r="P28" s="3" t="n"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -3690,7 +3706,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>latex 260 largo figuras perrito payaso globoflexia</t>
+          <t>latex metalico perlado brillo</t>
         </is>
       </c>
       <c r="U28" s="3" t="n"/>
@@ -3699,12 +3715,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-confeti-12-10</t>
+          <t>globo-latex-12-cromado-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Globo transparente con confeti 12", bolsa 10 pzas</t>
+          <t>Globo de látex cromado 12", bolsa 25 pzas</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3714,39 +3730,39 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Bodas y aniversarios, XV años, Baby shower</t>
+          <t>Bodas y aniversarios, XV años, Graduación, Navidad</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>bolsa con 25 piezas</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Globo transparente que ya trae confeti metálico dentro. Al inflarlo y frotarlo, el confeti se pega a las paredes.</t>
+          <t>Efecto espejo, parecido al foil pero en látex. Para decoraciones de lujo y arcos de evento.</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 10 globos con confeti incluido</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 25 piezas; Acabado: Cromado tipo espejo</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Dorado, Plateado, Oro rosa, Rosa, Azul</t>
+          <t>Oro cromo #c9a227, Plata cromo #a9b1bb, Oro rosa cromo #d9897a, Champagne cromo #d8c08f, Azul cromo #3767c9</t>
         </is>
       </c>
       <c r="M29" s="3" t="n"/>
@@ -3760,7 +3776,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3770,7 +3786,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>latex confeti transparente brillos</t>
+          <t>latex cromado cromo espejo lujo</t>
         </is>
       </c>
       <c r="U29" s="3" t="n"/>
@@ -3779,12 +3795,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-corazon-12-50</t>
+          <t>globo-latex-5-mini-100</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex corazón 12", bolsa 50 pzas</t>
+          <t>Globo de látex 5" mini, bolsa 100 pzas</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3794,39 +3810,39 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Amor y amistad, Bodas y aniversarios, XV años</t>
+          <t>Baby shower, Cumpleaños, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 100 piezas</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Globos de látex en forma de corazón para San Valentín, bodas y declaraciones.</t>
+          <t>Globito de 5 pulgadas para dar textura a arcos orgánicos, rellenar burbujas y decorar mesas.</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas</t>
+          <t>Medida: 5 in (13 cm) inflado; Contenido: 100 piezas; Material: Látex natural</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Fucsia, Blanco</t>
+          <t>Rosa, Rojo, Azul rey, Verde limón, Lila, Amarillo, Blanco, Negro</t>
         </is>
       </c>
       <c r="M30" s="3" t="n"/>
@@ -3850,7 +3866,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>latex corazon corazones amor san valentin</t>
+          <t>latex mini 5 pulgadas chico arco organico relleno</t>
         </is>
       </c>
       <c r="U30" s="3" t="n"/>
@@ -3859,12 +3875,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-feliz-cumple-12-50</t>
+          <t>globo-latex-18-10</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex impreso "Feliz Cumple", bolsa 50 pzas</t>
+          <t>Globo de látex 18", bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -3874,37 +3890,41 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles</t>
+          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Globos de 12 pulgadas en colores surtidos con "Feliz Cumpleaños" impreso alrededor.</t>
+          <t>Globo grande de 18 pulgadas para dar volumen en arcos y columnas.</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas en colores surtidos; Impresión: A una tinta, todo alrededor</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n"/>
+          <t>Medida: 18 in (45 cm) inflado; Contenido: 10 piezas; Material: Látex natural</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Azul cielo, Rosa, Rojo, Amarillo, Blanco, Negro</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="n"/>
@@ -3926,7 +3946,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>latex impreso feliz cumpleaños cumple surtido</t>
+          <t>latex 18 pulgadas grande arco columna</t>
         </is>
       </c>
       <c r="U31" s="3" t="n"/>
@@ -3935,12 +3955,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>globo-latex-36-gigante</t>
+          <t>globo-latex-260-50</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Globo de látex gigante 36"</t>
+          <t>Globo de látex 260 para figuras, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3950,39 +3970,39 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Revelación de género, Bodas y aniversarios</t>
+          <t>Fiestas infantiles, Cumpleaños</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Globo de 3 pies (90 cm) para fotos, revelaciones de género y como pieza central de una decoración.</t>
+          <t>Globo largo para hacer perritos, espadas, flores y figuras. Se infla con inflador manual.</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Medida: 36 in (90 cm) inflado; Material: Látex natural grueso</t>
+          <t>Medida: 5 × 150 cm inflado (260Q); Contenido: 50 piezas; Inflado: Con inflador manual</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Rosa, Rojo, Azul cielo, Dorado, Blanco, Negro</t>
+          <t>Surtido, Blanco, Rojo, Azul, Verde, Amarillo, Negro</t>
         </is>
       </c>
       <c r="M32" s="3" t="n"/>
@@ -4006,7 +4026,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>latex gigante 36 jumbo grande revelacion</t>
+          <t>latex 260 largo figuras perrito payaso globoflexia</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
@@ -4015,12 +4035,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>kit-arco-organico</t>
+          <t>globo-latex-confeti-12-10</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Kit arco orgánico de globos (100 pzas)</t>
+          <t>Globo transparente con confeti 12", bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4030,59 +4050,55 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Baby shower, Cumpleaños, Bodas y aniversarios, XV años, Revelación de género</t>
+          <t>Cumpleaños, Bodas y aniversarios, XV años, Baby shower</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Todo para armar un arco orgánico de 2.5 a 3 metros: 100 globos en tres tamaños, cinta para arco y puntos de pegamento.</t>
+          <t>Globo transparente que ya trae confeti metálico dentro. Al inflarlo y frotarlo, el confeti se pega a las paredes.</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Incluye: 100 globos (5", 10" y 12"), 5 m de cinta y 1 rollo de puntos de pegamento; Largo aproximado: 2.5 a 3 m</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Paleta</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Rosa y dorado, Azul y plata, Pastel arcoíris, Salvia y blanco, Negro y dorado</t>
-        </is>
-      </c>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 10 globos con confeti incluido</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Oro rosa, Rosa, Azul</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="n"/>
       <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -4090,7 +4106,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>kit arco organico guirnalda decoracion set</t>
+          <t>latex confeti transparente brillos</t>
         </is>
       </c>
       <c r="U33" s="3" t="n"/>
@@ -4099,12 +4115,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>inflador-manual-doble-accion</t>
+          <t>globo-latex-corazon-12-50</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Inflador manual de doble acción</t>
+          <t>Globo de látex corazón 12", bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4112,37 +4128,41 @@
           <t>Globos de látex</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Amor y amistad, Bodas y aniversarios, XV años</t>
+        </is>
+      </c>
       <c r="E34" s="4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Infla al subir y al bajar, así terminas el doble de rápido. Sirve para látex, globos 260 y foil con aire.</t>
+          <t>Globos de látex en forma de corazón para San Valentín, bodas y declaraciones.</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Largo: 30 cm; Uso: Látex, 260 y foil chico; Incluye: Boquilla para globo 260</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Azul, Rosa, Morado</t>
+          <t>Rojo, Rosa, Fucsia, Blanco</t>
         </is>
       </c>
       <c r="M34" s="3" t="n"/>
@@ -4166,7 +4186,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>inflador bomba accesorio herramienta</t>
+          <t>latex corazon corazones amor san valentin</t>
         </is>
       </c>
       <c r="U34" s="3" t="n"/>
@@ -4175,12 +4195,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>cinta-para-arco-5m</t>
+          <t>globo-latex-feliz-cumple-12-50</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Cinta para arco de globos, 5 m</t>
+          <t>Globo de látex impreso "Feliz Cumple", bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4188,32 +4208,36 @@
           <t>Globos de látex</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Fiestas infantiles</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>rollo de 5 m</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Tira de plástico con orificios para insertar los nudos de los globos y armar arcos y guirnaldas sin pegamento.</t>
+          <t>Globos de 12 pulgadas en colores surtidos con "Feliz Cumpleaños" impreso alrededor.</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Largo: 5 m; Material: PVC transparente</t>
+          <t>Medida: 12 in (30 cm) inflado; Contenido: 50 piezas en colores surtidos; Impresión: A una tinta, todo alrededor</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -4238,7 +4262,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>cinta arco tira accesorio guirnalda</t>
+          <t>latex impreso feliz cumpleaños cumple surtido</t>
         </is>
       </c>
       <c r="U35" s="3" t="n"/>
@@ -4247,54 +4271,54 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>papel-china-50-pliegos</t>
+          <t>globo-latex-36-gigante</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Papel china, paquete 50 pliegos</t>
+          <t>Globo de látex gigante 36"</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
+          <t>Globos de látex</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Fiestas patrias, Navidad, Cumpleaños, Fiestas infantiles</t>
+          <t>Cumpleaños, Baby shower, Revelación de género, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>paquete con 50 pliegos</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Papel de china para piñatas, papel picado, flores, borlas y manualidades. Paquete de 50 pliegos de un solo color.</t>
+          <t>Globo de 3 pies (90 cm) para fotos, revelaciones de género y como pieza central de una decoración.</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Medida del pliego: 50 × 75 cm; Contenido: 50 pliegos</t>
+          <t>Medida: 36 in (90 cm) inflado; Material: Látex natural grueso</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Rosa, Fucsia, Rojo, Naranja, Amarillo, Verde bandera, Verde limón, Azul cielo, Azul rey, Morado, Blanco, Negro</t>
+          <t>Rosa, Rojo, Azul cielo, Dorado, Blanco, Negro</t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
@@ -4303,7 +4327,7 @@
       <c r="P36" s="3" t="n"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -4318,7 +4342,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>papel china piñata manualidades pliegos</t>
+          <t>latex gigante 36 jumbo grande revelacion</t>
         </is>
       </c>
       <c r="U36" s="3" t="n"/>
@@ -4327,68 +4351,72 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>papel-crepe-pliego</t>
+          <t>kit-arco-organico</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Papel crepé, pliego 50 × 200 cm</t>
+          <t>Kit arco orgánico de globos (100 pzas)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
+          <t>Globos de látex</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Fiestas infantiles, Fiestas patrias, Navidad</t>
+          <t>Baby shower, Cumpleaños, Bodas y aniversarios, XV años, Revelación de género</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7</v>
+        <v>235</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>35</v>
+        <v>420</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Papel crepé elástico para flores, disfraces, cortinas y forrar mesas.</t>
+          <t>Todo para armar un arco orgánico de 2.5 a 3 metros: 100 globos en tres tamaños, cinta para arco y puntos de pegamento.</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 200 cm; Textura: Corrugado elástico</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t>Incluye: 100 globos (5", 10" y 12"), 5 m de cinta y 1 rollo de puntos de pegamento; Largo aproximado: 2.5 a 3 m</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Paleta</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Rosa y dorado, Azul y plata, Pastel arcoíris, Salvia y blanco, Negro y dorado</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="n"/>
       <c r="P37" s="3" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -4398,7 +4426,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>papel crepe crepé flores disfraz manualidades</t>
+          <t>kit arco organico guirnalda decoracion set</t>
         </is>
       </c>
       <c r="U37" s="3" t="n"/>
@@ -4407,50 +4435,50 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>cartulina-pliego</t>
+          <t>inflador-manual-doble-accion</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Cartulina, pliego 50 × 65 cm</t>
+          <t>Inflador manual de doble acción</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
+          <t>Globos de látex</t>
         </is>
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="4" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F38" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>25</v>
-      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Cartulina de colores para letreros, carteles, tareas y manualidades.</t>
+          <t>Infla al subir y al bajar, así terminas el doble de rápido. Sirve para látex, globos 260 y foil con aire.</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 65 cm; Gramaje: 180 g/m² aprox.</t>
+          <t>Largo: 30 cm; Uso: Látex, 260 y foil chico; Incluye: Boquilla para globo 260</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Amarillo, Rosa, Rojo, Verde, Azul cielo, Azul rey, Naranja, Morado, Blanco, Negro</t>
+          <t>Azul, Rosa, Morado</t>
         </is>
       </c>
       <c r="M38" s="3" t="n"/>
@@ -4474,7 +4502,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>cartulina carteles letrero escolar</t>
+          <t>inflador bomba accesorio herramienta</t>
         </is>
       </c>
       <c r="U38" s="3" t="n"/>
@@ -4483,67 +4511,55 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>papel-picado-plastico-5m</t>
+          <t>cinta-para-arco-5m</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Papel picado de plástico, tira 5 m</t>
+          <t>Cinta para arco de globos, 5 m</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Papelería</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Navidad, Fiestas patrias, Bodas y aniversarios, XV años, Cumpleaños</t>
-        </is>
-      </c>
+          <t>Globos de látex</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n"/>
       <c r="E39" s="4" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>tira de 5 m</t>
+          <t>rollo de 5 m</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Papel picado de plástico resistente al aire y la lluvia, para posadas, patios y salones. Tira de 5 metros con 10 pliegos.</t>
+          <t>Tira de plástico con orificios para insertar los nudos de los globos y armar arcos y guirnaldas sin pegamento.</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Largo: 5 m con 10 pliegos; Material: Plástico, se puede reusar</t>
+          <t>Largo: 5 m; Material: PVC transparente</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Multicolor, Navidad, Tricolor, Blanco y dorado</t>
-        </is>
-      </c>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -4558,7 +4574,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>papel picado plastico posada navidad fiestas patrias</t>
+          <t>cinta arco tira accesorio guirnalda</t>
         </is>
       </c>
       <c r="U39" s="3" t="n"/>
@@ -4567,12 +4583,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>banderin-feliz-cumpleanos</t>
+          <t>papel-china-50-pliegos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Banderín "Feliz Cumpleaños", 2.5 m</t>
+          <t>Papel china, paquete 50 pliegos</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -4582,59 +4598,55 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles</t>
+          <t>Fiestas patrias, Navidad, Cumpleaños, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>paquete con 50 pliegos</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Guirnalda de banderines con la frase "Feliz Cumpleaños", ya armada con cordón.</t>
+          <t>Papel de china para piñatas, papel picado, flores, borlas y manualidades. Paquete de 50 pliegos de un solo color.</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Largo: 2.5 m; Material: Cartulina gruesa</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Multicolor, Rosa, Azul</t>
-        </is>
-      </c>
+          <t>Medida del pliego: 50 × 75 cm; Contenido: 50 pliegos</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Rosa, Fucsia, Rojo, Naranja, Amarillo, Verde bandera, Verde limón, Azul cielo, Azul rey, Morado, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -4642,7 +4654,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>banderin guirnalda letrero feliz cumpleaños</t>
+          <t>papel china piñata manualidades pliegos</t>
         </is>
       </c>
       <c r="U40" s="3" t="n"/>
@@ -4651,12 +4663,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>invitaciones-paquete-10</t>
+          <t>papel-crepe-pliego</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Invitaciones con sobre, paquete 10</t>
+          <t>Papel crepé, pliego 50 × 200 cm</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4666,47 +4678,43 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, XV años, Bodas y aniversarios</t>
+          <t>Fiestas infantiles, Fiestas patrias, Navidad</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>paquete con 10 invitaciones</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Invitaciones impresas para llenar a mano, con sobre. Elige el diseño de tu evento.</t>
+          <t>Papel crepé elástico para flores, disfraces, cortinas y forrar mesas.</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Medida: 10 × 15 cm; Contenido: 10 invitaciones y 10 sobres</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños infantil, Baby shower, XV años, Boda</t>
-        </is>
-      </c>
+          <t>Medida: 50 × 200 cm; Textura: Corrugado elástico</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="n"/>
       <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
@@ -4726,7 +4734,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>invitaciones invitacion sobre tarjetas</t>
+          <t>papel crepe crepé flores disfraz manualidades</t>
         </is>
       </c>
       <c r="U41" s="3" t="n"/>
@@ -4735,12 +4743,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>foami-carta-10</t>
+          <t>cartulina-pliego</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Foami tamaño carta, paquete 10 hojas</t>
+          <t>Cartulina, pliego 50 × 65 cm</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -4748,41 +4756,37 @@
           <t>Papelería</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Fiestas infantiles</t>
-        </is>
-      </c>
+      <c r="D42" s="3" t="n"/>
       <c r="E42" s="4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>paquete con 10 hojas</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Hojas de foami de 2 mm para manualidades, letreros y decoración escolar.</t>
+          <t>Cartulina de colores para letreros, carteles, tareas y manualidades.</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Medida: Carta (21.5 × 28 cm); Grosor: 2 mm; Contenido: 10 hojas</t>
+          <t>Medida: 50 × 65 cm; Gramaje: 180 g/m² aprox.</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro, Café</t>
+          <t>Amarillo, Rosa, Rojo, Verde, Azul cielo, Azul rey, Naranja, Morado, Blanco, Negro</t>
         </is>
       </c>
       <c r="M42" s="3" t="n"/>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>foami fomi goma eva manualidades escolar</t>
+          <t>cartulina carteles letrero escolar</t>
         </is>
       </c>
       <c r="U42" s="3" t="n"/>
@@ -4815,12 +4819,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>foami-diamantado-carta-5</t>
+          <t>papel-picado-plastico-5m</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Foami diamantado carta, paquete 5 hojas</t>
+          <t>Papel picado de plástico, tira 5 m</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -4830,55 +4834,59 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>XV años, Navidad, Fiestas infantiles</t>
+          <t>Navidad, Fiestas patrias, Bodas y aniversarios, XV años, Cumpleaños</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>paquete con 5 hojas</t>
+          <t>tira de 5 m</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Foami con brillantina que no se cae. Para coronas, letreros y adornos con brillo.</t>
+          <t>Papel picado de plástico resistente al aire y la lluvia, para posadas, patios y salones. Tira de 5 metros con 10 pliegos.</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Medida: Carta (21.5 × 28 cm); Contenido: 5 hojas</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rosa, Rojo, Azul, Morado, Verde</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+          <t>Largo: 5 m con 10 pliegos; Material: Plástico, se puede reusar</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Multicolor, Navidad, Tricolor, Blanco y dorado</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n"/>
       <c r="Q43" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -4886,7 +4894,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>foami diamantado brillantina glitter escarchado</t>
+          <t>papel picado plastico posada navidad fiestas patrias</t>
         </is>
       </c>
       <c r="U43" s="3" t="n"/>
@@ -4895,12 +4903,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>papel-metalico-pliego</t>
+          <t>banderin-feliz-cumpleanos</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Papel metálico, pliego 50 × 70 cm</t>
+          <t>Banderín "Feliz Cumpleaños", 2.5 m</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4910,43 +4918,47 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Graduación</t>
+          <t>Cumpleaños, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>pliego</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Papel con acabado espejo para forrar cajas, hacer moños y decorar fondos.</t>
+          <t>Guirnalda de banderines con la frase "Feliz Cumpleaños", ya armada con cordón.</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 70 cm; Acabado: Metálico brillante</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+          <t>Largo: 2.5 m; Material: Cartulina gruesa</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Multicolor, Rosa, Azul</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n"/>
       <c r="Q44" s="3" t="inlineStr">
@@ -4966,7 +4978,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>papel metalico espejo lustre brillante</t>
+          <t>banderin guirnalda letrero feliz cumpleaños</t>
         </is>
       </c>
       <c r="U44" s="3" t="n"/>
@@ -4975,12 +4987,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>topper-feliz-cumple</t>
+          <t>invitaciones-paquete-10</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Topper para pastel "Feliz Cumple"</t>
+          <t>Invitaciones con sobre, paquete 10</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -4990,43 +5002,47 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, XV años, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>paquete con 10 invitaciones</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Adorno para pastel de cartulina metálica, con palitos para insertar.</t>
+          <t>Invitaciones impresas para llenar a mano, con sobre. Elige el diseño de tu evento.</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Medida: 15 × 12 cm; Material: Cartulina metálica</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Oro rosa, Negro</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+          <t>Medida: 10 × 15 cm; Contenido: 10 invitaciones y 10 sobres</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños infantil, Baby shower, XV años, Boda</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="inlineStr">
@@ -5046,7 +5062,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>topper pastel adorno cake</t>
+          <t>invitaciones invitacion sobre tarjetas</t>
         </is>
       </c>
       <c r="U45" s="3" t="n"/>
@@ -5055,67 +5071,63 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>papel-envolver-rollo-5m</t>
+          <t>foami-carta-10</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Papel para envolver, rollo 70 cm × 5 m</t>
+          <t>Foami tamaño carta, paquete 10 hojas</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Fiestas infantiles</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>paquete con 10 hojas</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Papel para regalo en rollo con tubo de cartón. Alcanza para envolver de 8 a 10 regalos medianos.</t>
+          <t>Hojas de foami de 2 mm para manualidades, letreros y decoración escolar.</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Medida: 70 cm × 5 m; Papel: Couché 60 g/m²</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Medida: Carta (21.5 × 28 cm); Grosor: 2 mm; Contenido: 10 hojas</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Amarillo, Verde, Azul, Morado, Naranja, Blanco, Negro, Café</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -5130,7 +5142,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>papel envolver regalo rollo envoltura</t>
+          <t>foami fomi goma eva manualidades escolar</t>
         </is>
       </c>
       <c r="U46" s="3" t="n"/>
@@ -5139,62 +5151,58 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>papel-envolver-pliegos-25</t>
+          <t>foami-diamantado-carta-5</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Papel para envolver, paquete 25 pliegos</t>
+          <t>Foami diamantado carta, paquete 5 hojas</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>XV años, Navidad, Fiestas infantiles</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>paquete con 25 pliegos</t>
+          <t>paquete con 5 hojas</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Pliegos para regalo del mismo diseño, ideales para tiendas y mesas de regalos.</t>
+          <t>Foami con brillantina que no se cae. Para coronas, letreros y adornos con brillo.</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Medida del pliego: 70 × 100 cm; Contenido: 25 pliegos</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Medida: Carta (21.5 × 28 cm); Contenido: 5 hojas</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rosa, Rojo, Azul, Morado, Verde</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
       <c r="O47" s="3" t="n"/>
       <c r="P47" s="3" t="n"/>
       <c r="Q47" s="3" t="inlineStr">
@@ -5214,7 +5222,7 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>papel envolver regalo pliegos mayoreo</t>
+          <t>foami diamantado brillantina glitter escarchado</t>
         </is>
       </c>
       <c r="U47" s="3" t="n"/>
@@ -5223,52 +5231,56 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>papel-kraft-rollo-10m</t>
+          <t>papel-metalico-pliego</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Papel kraft, rollo 90 cm × 10 m</t>
+          <t>Papel metálico, pliego 50 × 70 cm</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, Navidad</t>
+          <t>Navidad, Graduación</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>pliego</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1100</v>
+        <v>30</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Papel kraft natural para envolturas rústicas, manteles de mesa de postres y empaques.</t>
+          <t>Papel con acabado espejo para forrar cajas, hacer moños y decorar fondos.</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Medida: 90 cm × 10 m; Gramaje: 80 g/m²</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="n"/>
+          <t>Medida: 50 × 70 cm; Acabado: Metálico brillante</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
+        </is>
+      </c>
       <c r="M48" s="3" t="n"/>
       <c r="N48" s="3" t="n"/>
       <c r="O48" s="3" t="n"/>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>papel kraft estraza rustico empaque</t>
+          <t>papel metalico espejo lustre brillante</t>
         </is>
       </c>
       <c r="U48" s="3" t="n"/>
@@ -5299,54 +5311,54 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>mono-grande-bolsa-10</t>
+          <t>topper-feliz-cumple</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Moño grande para regalo, bolsa 10 pzas</t>
+          <t>Topper para pastel "Feliz Cumple"</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Envolturas</t>
+          <t>Papelería</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad, Bodas y aniversarios, Amor y amistad</t>
+          <t>Cumpleaños</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 10 piezas</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Moños de listón satinado ya armados, con adhesivo en la base.</t>
+          <t>Adorno para pastel de cartulina metálica, con palitos para insertar.</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Diámetro: 12 cm; Contenido: 10 moños del mismo color</t>
+          <t>Medida: 15 × 12 cm; Material: Cartulina metálica</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Rojo, Rosa, Dorado, Plateado, Azul, Morado, Blanco, Verde</t>
+          <t>Dorado, Plateado, Oro rosa, Negro</t>
         </is>
       </c>
       <c r="M49" s="3" t="n"/>
@@ -5370,7 +5382,7 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>moño moños regalo listón adhesivo</t>
+          <t>topper pastel adorno cake</t>
         </is>
       </c>
       <c r="U49" s="3" t="n"/>
@@ -5379,12 +5391,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>mono-estrella-bolsa-50</t>
+          <t>papel-envolver-rollo-5m</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Moño estrella chico, bolsa 50 pzas</t>
+          <t>Papel para envolver, rollo 70 cm × 5 m</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5394,7 +5406,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Cumpleaños</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -5404,45 +5416,49 @@
         <v>38</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>bolsa con 50 piezas</t>
+          <t>rollo</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Moño estrella metálico de 6 cm con adhesivo, para regalos pequeños y bolsas.</t>
+          <t>Papel para regalo en rollo con tubo de cartón. Alcanza para envolver de 8 a 10 regalos medianos.</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Diámetro: 6 cm; Contenido: 50 moños</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
+          <t>Medida: 70 cm × 5 m; Papel: Couché 60 g/m²</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="n"/>
       <c r="P50" s="3" t="n"/>
       <c r="Q50" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -5450,7 +5466,7 @@
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>moño estrella chico regalo metalico</t>
+          <t>papel envolver regalo rollo envoltura</t>
         </is>
       </c>
       <c r="U50" s="3" t="n"/>
@@ -5459,12 +5475,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>liston-satinado-1in-20m</t>
+          <t>papel-envolver-pliegos-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Listón satinado 1", rollo 20 m</t>
+          <t>Papel para envolver, paquete 25 pliegos</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5474,43 +5490,47 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Bodas y aniversarios, XV años, Navidad, Amor y amistad</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>rollo de 20 m</t>
+          <t>paquete con 25 pliegos</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Listón satinado de doble cara para moños, recuerdos, arreglos florales y envolturas.</t>
+          <t>Pliegos para regalo del mismo diseño, ideales para tiendas y mesas de regalos.</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Ancho: 1 in (2.5 cm); Largo: 20 m</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Fucsia, Dorado, Plateado, Azul rey, Azul cielo, Verde, Blanco, Negro, Morado, Vino</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
+          <t>Medida del pliego: 70 × 100 cm; Contenido: 25 pliegos</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O51" s="3" t="n"/>
       <c r="P51" s="3" t="n"/>
       <c r="Q51" s="3" t="inlineStr">
@@ -5530,7 +5550,7 @@
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>liston satinado moño cinta recuerdos</t>
+          <t>papel envolver regalo pliegos mayoreo</t>
         </is>
       </c>
       <c r="U51" s="3" t="n"/>
@@ -5539,12 +5559,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>liston-rizar-100m</t>
+          <t>papel-kraft-rollo-10m</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Listón para rizar, rollo 100 m</t>
+          <t>Papel kraft, rollo 90 cm × 10 m</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -5554,41 +5574,37 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad</t>
+          <t>Bodas y aniversarios, Navidad</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>rollo de 100 m</t>
+          <t>rollo</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>90</v>
+        <v>1100</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Listón de rafia que se riza con tijera. Sirve para amarrar globos y decorar regalos.</t>
+          <t>Papel kraft natural para envolturas rústicas, manteles de mesa de postres y empaques.</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Ancho: 3/16 in (5 mm); Largo: 100 m</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Rosa, Dorado, Plateado, Azul, Verde, Morado, Blanco</t>
-        </is>
-      </c>
+          <t>Medida: 90 cm × 10 m; Gramaje: 80 g/m²</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n"/>
       <c r="M52" s="3" t="n"/>
       <c r="N52" s="3" t="n"/>
       <c r="O52" s="3" t="n"/>
@@ -5610,7 +5626,7 @@
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>liston rizar rafia globos amarrar</t>
+          <t>papel kraft estraza rustico empaque</t>
         </is>
       </c>
       <c r="U52" s="3" t="n"/>
@@ -5619,12 +5635,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>bolsa-regalo-mediana</t>
+          <t>mono-grande-bolsa-10</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de regalo mediana 26 × 32 cm</t>
+          <t>Moño grande para regalo, bolsa 10 pzas</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -5634,52 +5650,48 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Cumpleaños, Navidad, Bodas y aniversarios, Amor y amistad</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 10 piezas</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Bolsa de papel con asas de cordón y refuerzo en la base.</t>
+          <t>Moños de listón satinado ya armados, con adhesivo en la base.</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Medida: 26 × 32 × 12 cm; Asas: Cordón</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Diámetro: 12 cm; Contenido: 10 moños del mismo color</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Dorado, Plateado, Azul, Morado, Blanco, Verde</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
       <c r="O53" s="3" t="n"/>
       <c r="P53" s="3" t="n"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -5694,7 +5706,7 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>bolsa regalo mediana asas</t>
+          <t>moño moños regalo listón adhesivo</t>
         </is>
       </c>
       <c r="U53" s="3" t="n"/>
@@ -5703,12 +5715,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>bolsa-regalo-grande</t>
+          <t>mono-estrella-bolsa-50</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de regalo grande 33 × 45 cm</t>
+          <t>Moño estrella chico, bolsa 50 pzas</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -5718,21 +5730,21 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Navidad, Cumpleaños</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>pieza</t>
+          <t>bolsa con 50 piezas</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5740,25 +5752,21 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Bolsa grande para peluches, ropa y regalos voluminosos.</t>
+          <t>Moño estrella metálico de 6 cm con adhesivo, para regalos pequeños y bolsas.</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Medida: 33 × 45 × 15 cm; Asas: Cordón</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="n"/>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
-        </is>
-      </c>
+          <t>Diámetro: 6 cm; Contenido: 50 moños</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rojo, Verde, Azul, Rosa</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="3" t="n"/>
       <c r="O54" s="3" t="n"/>
       <c r="P54" s="3" t="n"/>
       <c r="Q54" s="3" t="inlineStr">
@@ -5778,7 +5786,7 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>bolsa regalo grande asas peluche</t>
+          <t>moño estrella chico regalo metalico</t>
         </is>
       </c>
       <c r="U54" s="3" t="n"/>
@@ -5787,12 +5795,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>bolsa-celofan-15x25-100</t>
+          <t>liston-satinado-1in-20m</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Bolsa de celofán 15 × 25 cm, paquete 100</t>
+          <t>Listón satinado 1", rollo 20 m</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5802,37 +5810,41 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Fiestas infantiles, Navidad</t>
+          <t>Bodas y aniversarios, XV años, Navidad, Amor y amistad</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>paquete con 100 bolsas</t>
+          <t>rollo de 20 m</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Bolsitas transparentes para dulceros, aguinaldos de posada, galletas y recuerdos.</t>
+          <t>Listón satinado de doble cara para moños, recuerdos, arreglos florales y envolturas.</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Medida: 15 × 25 cm; Contenido: 100 bolsas</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="n"/>
+          <t>Ancho: 1 in (2.5 cm); Largo: 20 m</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Rosa, Fucsia, Dorado, Plateado, Azul rey, Azul cielo, Verde, Blanco, Negro, Morado, Vino</t>
+        </is>
+      </c>
       <c r="M55" s="3" t="n"/>
       <c r="N55" s="3" t="n"/>
       <c r="O55" s="3" t="n"/>
@@ -5854,7 +5866,7 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>bolsa celofan dulcero dulces aguinaldo posada galletas recuerdos</t>
+          <t>liston satinado moño cinta recuerdos</t>
         </is>
       </c>
       <c r="U55" s="3" t="n"/>
@@ -5863,12 +5875,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>celofan-rollo-1x20m</t>
+          <t>liston-rizar-100m</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Papel celofán, rollo 1 × 20 m</t>
+          <t>Listón para rizar, rollo 100 m</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -5878,39 +5890,39 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Amor y amistad</t>
+          <t>Cumpleaños, Navidad</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>rollo</t>
+          <t>rollo de 100 m</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Celofán para envolver canastas, arcones, arreglos y ramos.</t>
+          <t>Listón de rafia que se riza con tijera. Sirve para amarrar globos y decorar regalos.</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Medida: 1 × 20 m; Calibre: Grueso, no se rompe al doblar</t>
+          <t>Ancho: 3/16 in (5 mm); Largo: 100 m</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Transparente, Rojo #e63946, Rosa, Azul, Verde</t>
+          <t>Rojo, Rosa, Dorado, Plateado, Azul, Verde, Morado, Blanco</t>
         </is>
       </c>
       <c r="M56" s="3" t="n"/>
@@ -5934,7 +5946,7 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>celofan rollo canasta arcon arreglo transparente</t>
+          <t>liston rizar rafia globos amarrar</t>
         </is>
       </c>
       <c r="U56" s="3" t="n"/>
@@ -5943,12 +5955,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>caja-regalo-set-3</t>
+          <t>bolsa-regalo-mediana</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Cajas de regalo con tapa, set de 3</t>
+          <t>Bolsa de regalo mediana 26 × 32 cm</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -5958,55 +5970,59 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>set de 3 cajas</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>650</v>
+        <v>75</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Tres cajas rígidas con tapa que se guardan una dentro de otra. Incluyen listón decorativo.</t>
+          <t>Bolsa de papel con asas de cordón y refuerzo en la base.</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>Medidas: 25 × 25, 20 × 20 y 15 × 15 cm; Material: Cartón rígido forrado</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>Rojo, Kraft, Blanco, Rosa, Negro, Azul rey</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
+          <t>Medida: 26 × 32 × 12 cm; Asas: Cordón</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O57" s="3" t="n"/>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
           <t>Visible</t>
@@ -6014,7 +6030,7 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>caja cajas regalo tapa set</t>
+          <t>bolsa regalo mediana asas</t>
         </is>
       </c>
       <c r="U57" s="3" t="n"/>
@@ -6023,12 +6039,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>papel-seda-24-hojas</t>
+          <t>bolsa-regalo-grande</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Papel seda para regalo, paquete 24 hojas</t>
+          <t>Bolsa de regalo grande 33 × 45 cm</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6038,43 +6054,47 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Baby shower, Navidad, Amor y amistad, Bodas y aniversarios</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>paquete con 24 hojas</t>
+          <t>pieza</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Papel seda delgado para acomodar dentro de bolsas y cajas de regalo.</t>
+          <t>Bolsa grande para peluches, ropa y regalos voluminosos.</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Medida: 50 × 70 cm; Contenido: 24 hojas</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>Rosa pastel, Rosa, Rojo, Dorado, Azul cielo, Lila, Blanco, Negro</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="3" t="n"/>
+          <t>Medida: 33 × 45 × 15 cm; Asas: Cordón</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Infantil, Baby, Elegante negro y dorado, Navidad, Amor</t>
+        </is>
+      </c>
       <c r="O58" s="3" t="n"/>
       <c r="P58" s="3" t="n"/>
       <c r="Q58" s="3" t="inlineStr">
@@ -6094,7 +6114,7 @@
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>papel seda tissue relleno bolsa regalo</t>
+          <t>bolsa regalo grande asas peluche</t>
         </is>
       </c>
       <c r="U58" s="3" t="n"/>
@@ -6103,12 +6123,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>relleno-viruta-papel-100g</t>
+          <t>bolsa-celofan-15x25-100</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Relleno de viruta de papel, 100 g</t>
+          <t>Bolsa de celofán 15 × 25 cm, paquete 100</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6118,41 +6138,37 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Navidad, Amor y amistad, Bodas y aniversarios</t>
+          <t>Cumpleaños, Fiestas infantiles, Navidad</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>bolsa de 100 g</t>
+          <t>paquete con 100 bolsas</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Papel triturado para canastas, cajas de regalo y arcones navideños.</t>
+          <t>Bolsitas transparentes para dulceros, aguinaldos de posada, galletas y recuerdos.</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Contenido: 100 g; Material: Papel reciclado</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>Kraft, Blanco, Rosa, Rojo, Dorado, Negro, Verde, Azul</t>
-        </is>
-      </c>
+          <t>Medida: 15 × 25 cm; Contenido: 100 bolsas</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="n"/>
       <c r="M59" s="3" t="n"/>
       <c r="N59" s="3" t="n"/>
       <c r="O59" s="3" t="n"/>
@@ -6174,14 +6190,334 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>viruta relleno papel triturado canasta arcon</t>
+          <t>bolsa celofan dulcero dulces aguinaldo posada galletas recuerdos</t>
         </is>
       </c>
       <c r="U59" s="3" t="n"/>
       <c r="V59" s="3" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>celofan-rollo-1x20m</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Papel celofán, rollo 1 × 20 m</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Navidad, Amor y amistad</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>rollo</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Celofán para envolver canastas, arcones, arreglos y ramos.</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Medida: 1 × 20 m; Calibre: Grueso, no se rompe al doblar</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Transparente, Rojo #e63946, Rosa, Azul, Verde</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>celofan rollo canasta arcon arreglo transparente</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="n"/>
+      <c r="V60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>caja-regalo-set-3</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Cajas de regalo con tapa, set de 3</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Navidad, Amor y amistad, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>set de 3 cajas</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Tres cajas rígidas con tapa que se guardan una dentro de otra. Incluyen listón decorativo.</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Medidas: 25 × 25, 20 × 20 y 15 × 15 cm; Material: Cartón rígido forrado</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Rojo, Kraft, Blanco, Rosa, Negro, Azul rey</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>caja cajas regalo tapa set</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="n"/>
+      <c r="V61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>papel-seda-24-hojas</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Papel seda para regalo, paquete 24 hojas</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Baby shower, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>paquete con 24 hojas</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Papel seda delgado para acomodar dentro de bolsas y cajas de regalo.</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Medida: 50 × 70 cm; Contenido: 24 hojas</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Rosa pastel, Rosa, Rojo, Dorado, Azul cielo, Lila, Blanco, Negro</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>papel seda tissue relleno bolsa regalo</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="n"/>
+      <c r="V62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>relleno-viruta-papel-100g</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Relleno de viruta de papel, 100 g</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Envolturas</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Navidad, Amor y amistad, Bodas y aniversarios</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>bolsa de 100 g</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Papel triturado para canastas, cajas de regalo y arcones navideños.</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Contenido: 100 g; Material: Papel reciclado</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Kraft, Blanco, Rosa, Rojo, Dorado, Negro, Verde, Azul</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="3" t="n"/>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>viruta relleno papel triturado canasta arcon</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="n"/>
+      <c r="V63" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V59"/>
+  <autoFilter ref="A1:V63"/>
   <dataValidations count="8">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una de las categorías de la lista." type="list">
       <formula1>"Globos de foil,Globos de látex,Papelería,Envolturas"</formula1>
@@ -6219,7 +6555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D58"/>
+  <dimension ref="B1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6409,450 +6745,466 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>• Dos bolsas del mismo tamaño con distinta cantidad van en filas separadas, por ejemplo 18" (15 pz) y 18" (25 pz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>• Los productos con "Sempertex" en el nombre o con tonos de la carta muestran el logo de Sempertex y aparecen en la sección "Globos Sempertex".</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Fotos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>• Crea en Google Drive una carpeta "Fotos tienda" y súbelas ahí. De preferencia cuadradas, de unos 800 × 800 px.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>• Comparte la carpeta como "Cualquier persona con el enlace". Luego, en cada foto: clic derecho → Compartir → Copiar enlace, y pégalo en la columna Foto.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>• Crea en Google Drive una carpeta "Fotos tienda" y súbelas ahí. De preferencia cuadradas, de unos 800 × 800 px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>• Comparte la carpeta como "Cualquier persona con el enlace". Luego, en cada foto: clic derecho → Compartir → Copiar enlace, y pégalo en la columna Foto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
           <t>• Para una foto distinta por color usa la columna "Fotos por opción":  Dorado = enlace; Plateado = enlace</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="7" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>• Si un producto no tiene foto, la tienda muestra una ilustración con la leyenda "Imagen ilustrativa".</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Qué va en cada columna</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Columna</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Qué poner</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Ejemplo</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Identificador para el enlace del producto. Opcional: si lo dejas vacío se crea con el nombre. No lo cambies una vez publicado, porque lo usan los carritos y los enlaces compartidos. En un producto con varios tamaños, pon el mismo código en todas sus filas.</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>globo-foil-estrella-18</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Obligatorio. Nombre que ven los clientes.</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Globo foil estrella 18"</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Obligatorio. Una de: Globos de foil, Globos de látex, Papelería, Envolturas.</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Globos de foil</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Temáticas</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Separadas por comas. Si escribes una que no existe (por ejemplo "Día de las Madres"), la tienda la crea sola.</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Cumpleaños, Navidad</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Precio</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio. Precio de menudeo en pesos, solo el número.</t>
+          <t>Obligatorio. Una de: Globos de foil, Globos de látex, Papelería, Envolturas.</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Globos de foil</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
+          <t>Temáticas</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Separadas por comas. Si escribes una que no existe (por ejemplo "Día de las Madres"), la tienda la crea sola.</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Cumpleaños, Navidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Obligatorio. Precio de menudeo en pesos, solo el número.</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
           <t>Precio mayoreo</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Precio por unidad al llegar a la cantidad mínima. Déjalo vacío si no hay mayoreo.</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Mayoreo desde</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Cantidad mínima para el precio de mayoreo. Se suman todos los colores del mismo producto.</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>Se vende por</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Cómo se vende. Vacío = "pieza".</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>bolsa con 50 piezas</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Peso (g)</t>
+          <t>Mayoreo desde</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Gramos por unidad vendida. Se usa para calcular el envío; si falta se usan 100 g.</t>
+          <t>Cantidad mínima para el precio de mayoreo. Se suman todos los colores del mismo producto.</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
+          <t>Se vende por</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Cómo se vende. Vacío = "pieza".</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>bolsa con 50 piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Peso (g)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Gramos por unidad vendida. Se usa para calcular el envío; si falta se usan 100 g.</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Texto de la página del producto.</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Estrella metálica de 18 pulgadas…</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>Características</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Pares "Dato: valor" separados por punto y coma.</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>Medida: 18 in (45 cm); Material: Foil</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Colores</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Nombres separados por comas (ver pestaña Listas). Para otro color agrega su código: "Turquesa #1fb5ad".</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>Dorado, Plateado, Rosa</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
+          <t>Características</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Pares "Dato: valor" separados por punto y coma.</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Medida: 18 in (45 cm); Material: Foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Colores</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Nombres separados por comas (ver pestaña Listas). Para otro color agrega su código: "Turquesa #1fb5ad".</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Dorado, Plateado, Rosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
           <t>Otra opción</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Otra elección del cliente además del color: Número, Letra, Diseño, Tamaño…</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>Número</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Valores de la opción</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Separados por comas. Puedes usar rangos como 0-9 o A-Z.</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>0-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>Foto</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Enlace de Google Drive de la foto (compartida como "Cualquier persona con el enlace") o nombre de un archivo de la carpeta img. Vacío = ilustración.</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/…/view</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Fotos por opción</t>
+          <t>Valores de la opción</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Una foto por color u opción: "Dorado = enlace; Plateado = enlace".</t>
+          <t>Separados por comas. Puedes usar rangos como 0-9 o A-Z.</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Dorado = https://drive.google.com/file/d/…</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
+          <t>0-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Destacado</t>
+          <t>Foto</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Sí para mostrarlo en "Lo más pedido".</t>
+          <t>Enlace de Google Drive de la foto (compartida como "Cualquier persona con el enlace") o nombre de un archivo de la carpeta img. Vacío = ilustración.</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>https://drive.google.com/file/d/…/view</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Fotos por opción</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Sí para la etiqueta "Nuevo".</t>
+          <t>Una foto por color u opción: "Dorado = enlace; Plateado = enlace".</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
+          <t>Dorado = https://drive.google.com/file/d/…</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Destacado</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Visible, Agotado (se ve pero no se puede comprar) u Oculto (no aparece en la tienda).</t>
+          <t>Sí para mostrarlo en "Lo más pedido".</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Visible</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="B56" s="12" t="inlineStr">
         <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Sí para la etiqueta "Nuevo".</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Visible, Agotado (se ve pero no se puede comprar) u Oculto (no aparece en la tienda).</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
           <t>Palabras para buscar</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Otras palabras con las que los clientes buscan este producto.</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>metalico helio estrellas</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="B57" s="12" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Para vender un producto en varios tamaños: haz una fila por tamaño con el MISMO nombre y escribe aquí el tamaño (5", 12", 18"). Cada fila lleva su precio, mayoreo, peso y presentación; en la tienda se ven como un solo producto con selector de tamaño.</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>12"</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="B58" s="12" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>Colores agotados</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Colores o tonos sin existencia, separados por comas (nombres o códigos de la carta). En un producto con tamaños, aplica solo al tamaño de esa fila.</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>015, 390</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
